--- a/research/traditional_assets/database/data/new_zealand/new_zealand_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_electronics_general.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,13 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="B2">
+        <v>0.1213499452234936</v>
+      </c>
+      <c r="C2">
+        <v>100.1811531887268</v>
+      </c>
+      <c r="D2">
+        <v>94.4461531887268</v>
       </c>
       <c r="E2">
-        <v>-27.3</v>
+        <v>-25.845</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.455</v>
       </c>
       <c r="G2">
         <v>7.19</v>
@@ -1570,43 +1579,45 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.343089</v>
       </c>
       <c r="N2">
-        <v>-7.733333333333331</v>
+        <v>-8.076422333333332</v>
       </c>
       <c r="O2">
-        <v>-2.165333333333333</v>
+        <v>-2.261398253333333</v>
       </c>
       <c r="P2">
-        <v>-5.567999999999998</v>
+        <v>-5.815024079999999</v>
       </c>
       <c r="Q2">
-        <v>21.832</v>
+        <v>21.58497592</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S2">
+        <v>0.1051615446331701</v>
+      </c>
+      <c r="T2">
+        <v>1.370936365662127</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-Inf</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.2358</v>
+      </c>
+      <c r="V2">
+        <v>-6.311287547351657</v>
+      </c>
+      <c r="W2">
+        <v>1.724001603665521</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>-22.54031266911306</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1614,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1213499452234936</v>
+        <v>0.1232499452234936</v>
       </c>
       <c r="C3">
-        <v>100.1811531887268</v>
+        <v>96.40920266615694</v>
       </c>
       <c r="D3">
-        <v>94.4461531887268</v>
+        <v>92.12920266615694</v>
       </c>
       <c r="E3">
-        <v>-25.845</v>
+        <v>-24.39</v>
       </c>
       <c r="F3">
-        <v>1.455</v>
+        <v>2.91</v>
       </c>
       <c r="G3">
         <v>7.19</v>
@@ -1650,37 +1661,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M3">
-        <v>0.343089</v>
+        <v>0.6861780000000001</v>
       </c>
       <c r="N3">
-        <v>-8.076422333333332</v>
+        <v>-8.419511333333331</v>
       </c>
       <c r="O3">
-        <v>-2.261398253333333</v>
+        <v>-2.357463173333333</v>
       </c>
       <c r="P3">
-        <v>-5.815024079999999</v>
+        <v>-6.062048159999998</v>
       </c>
       <c r="Q3">
-        <v>21.58497592</v>
+        <v>21.33795184</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1051615446331701</v>
+        <v>0.1057672746804473</v>
       </c>
       <c r="T3">
-        <v>1.370936365662127</v>
+        <v>1.384925512250516</v>
       </c>
       <c r="U3">
         <v>0.2358</v>
       </c>
       <c r="V3">
-        <v>-6.311287547351657</v>
+        <v>-3.155643773675828</v>
       </c>
       <c r="W3">
-        <v>1.724001603665521</v>
+        <v>0.9799008018327604</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1688,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>-22.54031266911306</v>
+        <v>-11.27015633455653</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1696,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1232499452234936</v>
+        <v>0.1251499452234936</v>
       </c>
       <c r="C4">
-        <v>96.40920266615694</v>
+        <v>92.74820889297067</v>
       </c>
       <c r="D4">
-        <v>92.12920266615694</v>
+        <v>89.92320889297066</v>
       </c>
       <c r="E4">
-        <v>-24.39</v>
+        <v>-22.935</v>
       </c>
       <c r="F4">
-        <v>2.91</v>
+        <v>4.365</v>
       </c>
       <c r="G4">
         <v>7.19</v>
@@ -1732,37 +1743,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M4">
-        <v>0.6861780000000001</v>
+        <v>1.029267</v>
       </c>
       <c r="N4">
-        <v>-8.419511333333331</v>
+        <v>-8.762600333333332</v>
       </c>
       <c r="O4">
-        <v>-2.357463173333333</v>
+        <v>-2.453528093333333</v>
       </c>
       <c r="P4">
-        <v>-6.062048159999998</v>
+        <v>-6.309072239999999</v>
       </c>
       <c r="Q4">
-        <v>21.33795184</v>
+        <v>21.09092776</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1057672746804473</v>
+        <v>0.1063854940070499</v>
       </c>
       <c r="T4">
-        <v>1.384925512250516</v>
+        <v>1.399203094851037</v>
       </c>
       <c r="U4">
         <v>0.2358</v>
       </c>
       <c r="V4">
-        <v>-3.155643773675828</v>
+        <v>-2.103762515783886</v>
       </c>
       <c r="W4">
-        <v>0.9799008018327604</v>
+        <v>0.7318672012218402</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1770,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>-11.27015633455653</v>
+        <v>-7.51343755637102</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1778,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1251499452234936</v>
+        <v>0.1270499452234936</v>
       </c>
       <c r="C5">
-        <v>92.74820889297067</v>
+        <v>89.19038782119424</v>
       </c>
       <c r="D5">
-        <v>89.92320889297066</v>
+        <v>87.82038782119423</v>
       </c>
       <c r="E5">
-        <v>-22.935</v>
+        <v>-21.48</v>
       </c>
       <c r="F5">
-        <v>4.365</v>
+        <v>5.82</v>
       </c>
       <c r="G5">
         <v>7.19</v>
@@ -1814,37 +1825,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M5">
-        <v>1.029267</v>
+        <v>1.372356</v>
       </c>
       <c r="N5">
-        <v>-8.762600333333332</v>
+        <v>-9.105689333333331</v>
       </c>
       <c r="O5">
-        <v>-2.453528093333333</v>
+        <v>-2.549593013333333</v>
       </c>
       <c r="P5">
-        <v>-6.309072239999999</v>
+        <v>-6.556096319999998</v>
       </c>
       <c r="Q5">
-        <v>21.09092776</v>
+        <v>20.84390368</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1063854940070499</v>
+        <v>0.1070165929029566</v>
       </c>
       <c r="T5">
-        <v>1.399203094851037</v>
+        <v>1.413778127089069</v>
       </c>
       <c r="U5">
         <v>0.2358</v>
       </c>
       <c r="V5">
-        <v>-2.103762515783886</v>
+        <v>-1.577821886837914</v>
       </c>
       <c r="W5">
-        <v>0.7318672012218402</v>
+        <v>0.6078504009163802</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1852,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>-7.51343755637102</v>
+        <v>-5.635078167278264</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1860,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1270499452234936</v>
+        <v>0.1289499452234936</v>
       </c>
       <c r="C6">
-        <v>89.19038782119424</v>
+        <v>85.72866687373258</v>
       </c>
       <c r="D6">
-        <v>87.82038782119423</v>
+        <v>85.81366687373259</v>
       </c>
       <c r="E6">
-        <v>-21.48</v>
+        <v>-20.025</v>
       </c>
       <c r="F6">
-        <v>5.82</v>
+        <v>7.275</v>
       </c>
       <c r="G6">
         <v>7.19</v>
@@ -1896,37 +1907,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M6">
-        <v>1.372356</v>
+        <v>1.715445</v>
       </c>
       <c r="N6">
-        <v>-9.105689333333331</v>
+        <v>-9.448778333333332</v>
       </c>
       <c r="O6">
-        <v>-2.549593013333333</v>
+        <v>-2.645657933333333</v>
       </c>
       <c r="P6">
-        <v>-6.556096319999998</v>
+        <v>-6.803120399999998</v>
       </c>
       <c r="Q6">
-        <v>20.84390368</v>
+        <v>20.5968796</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1070165929029566</v>
+        <v>0.1076609780914088</v>
       </c>
       <c r="T6">
-        <v>1.413778127089069</v>
+        <v>1.428660002111059</v>
       </c>
       <c r="U6">
         <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>-1.577821886837914</v>
+        <v>-1.262257509470331</v>
       </c>
       <c r="W6">
-        <v>0.6078504009163802</v>
+        <v>0.5334403207331042</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1934,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>-5.635078167278264</v>
+        <v>-4.508062533822613</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1942,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1289499452234936</v>
+        <v>0.1308499452234936</v>
       </c>
       <c r="C7">
-        <v>85.72866687373258</v>
+        <v>82.35660547373242</v>
       </c>
       <c r="D7">
-        <v>85.81366687373259</v>
+        <v>83.89660547373242</v>
       </c>
       <c r="E7">
-        <v>-20.025</v>
+        <v>-18.57</v>
       </c>
       <c r="F7">
-        <v>7.275</v>
+        <v>8.73</v>
       </c>
       <c r="G7">
         <v>7.19</v>
@@ -1978,37 +1989,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M7">
-        <v>1.715445</v>
+        <v>2.058534</v>
       </c>
       <c r="N7">
-        <v>-9.448778333333332</v>
+        <v>-9.791867333333331</v>
       </c>
       <c r="O7">
-        <v>-2.645657933333333</v>
+        <v>-2.741722853333333</v>
       </c>
       <c r="P7">
-        <v>-6.803120399999998</v>
+        <v>-7.050144479999998</v>
       </c>
       <c r="Q7">
-        <v>20.5968796</v>
+        <v>20.34985552</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1076609780914088</v>
+        <v>0.1083190736030196</v>
       </c>
       <c r="T7">
-        <v>1.428660002111059</v>
+        <v>1.443858512771815</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>-1.262257509470331</v>
+        <v>-1.051881257891943</v>
       </c>
       <c r="W7">
-        <v>0.5334403207331042</v>
+        <v>0.4838336006109201</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -2016,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>-4.508062533822613</v>
+        <v>-3.756718778185509</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2024,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1308499452234936</v>
+        <v>0.1327499452234936</v>
       </c>
       <c r="C8">
-        <v>82.35660547373242</v>
+        <v>79.06832599333289</v>
       </c>
       <c r="D8">
-        <v>83.89660547373242</v>
+        <v>82.0633259933329</v>
       </c>
       <c r="E8">
-        <v>-18.57</v>
+        <v>-17.115</v>
       </c>
       <c r="F8">
-        <v>8.73</v>
+        <v>10.185</v>
       </c>
       <c r="G8">
         <v>7.19</v>
@@ -2060,37 +2071,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M8">
-        <v>2.058534</v>
+        <v>2.401623</v>
       </c>
       <c r="N8">
-        <v>-9.791867333333331</v>
+        <v>-10.13495633333333</v>
       </c>
       <c r="O8">
-        <v>-2.741722853333333</v>
+        <v>-2.837787773333333</v>
       </c>
       <c r="P8">
-        <v>-7.050144479999998</v>
+        <v>-7.297168559999998</v>
       </c>
       <c r="Q8">
-        <v>20.34985552</v>
+        <v>20.10283144</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1083190736030196</v>
+        <v>0.1089913217062778</v>
       </c>
       <c r="T8">
-        <v>1.443858512771815</v>
+        <v>1.4593838731242</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>-1.051881257891943</v>
+        <v>-0.9016125067645225</v>
       </c>
       <c r="W8">
-        <v>0.4838336006109201</v>
+        <v>0.4484002290950744</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -2098,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>-3.756718778185509</v>
+        <v>-3.220044667016152</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2106,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1327499452234936</v>
+        <v>0.1346499452234936</v>
       </c>
       <c r="C9">
-        <v>79.06832599333289</v>
+        <v>75.85845356212171</v>
       </c>
       <c r="D9">
-        <v>82.0633259933329</v>
+        <v>80.30845356212171</v>
       </c>
       <c r="E9">
-        <v>-17.115</v>
+        <v>-15.66</v>
       </c>
       <c r="F9">
-        <v>10.185</v>
+        <v>11.64</v>
       </c>
       <c r="G9">
         <v>7.19</v>
@@ -2142,37 +2153,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M9">
-        <v>2.401623</v>
+        <v>2.744712</v>
       </c>
       <c r="N9">
-        <v>-10.13495633333333</v>
+        <v>-10.47804533333333</v>
       </c>
       <c r="O9">
-        <v>-2.837787773333333</v>
+        <v>-2.933852693333333</v>
       </c>
       <c r="P9">
-        <v>-7.297168559999998</v>
+        <v>-7.544192639999998</v>
       </c>
       <c r="Q9">
-        <v>20.10283144</v>
+        <v>19.85580736</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1089913217062778</v>
+        <v>0.1096781838987374</v>
       </c>
       <c r="T9">
-        <v>1.4593838731242</v>
+        <v>1.475246741310333</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>-0.9016125067645223</v>
+        <v>-0.7889109434189571</v>
       </c>
       <c r="W9">
-        <v>0.4484002290950744</v>
+        <v>0.4218252004581901</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2180,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>-3.220044667016151</v>
+        <v>-2.817539083639132</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2188,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1346499452234936</v>
+        <v>0.1365499452234936</v>
       </c>
       <c r="C10">
-        <v>75.85845356212171</v>
+        <v>72.72206343684671</v>
       </c>
       <c r="D10">
-        <v>80.30845356212171</v>
+        <v>78.62706343684671</v>
       </c>
       <c r="E10">
-        <v>-15.66</v>
+        <v>-14.205</v>
       </c>
       <c r="F10">
-        <v>11.64</v>
+        <v>13.095</v>
       </c>
       <c r="G10">
         <v>7.19</v>
@@ -2224,37 +2235,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M10">
-        <v>2.744712</v>
+        <v>3.087801</v>
       </c>
       <c r="N10">
-        <v>-10.47804533333333</v>
+        <v>-10.82113433333333</v>
       </c>
       <c r="O10">
-        <v>-2.933852693333333</v>
+        <v>-3.029917613333333</v>
       </c>
       <c r="P10">
-        <v>-7.544192639999998</v>
+        <v>-7.791216719999997</v>
       </c>
       <c r="Q10">
-        <v>19.85580736</v>
+        <v>19.60878328</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1096781838987374</v>
+        <v>0.1103801419635587</v>
       </c>
       <c r="T10">
-        <v>1.475246741310333</v>
+        <v>1.491458243962095</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>-0.7889109434189571</v>
+        <v>-0.701254171927962</v>
       </c>
       <c r="W10">
-        <v>0.4218252004581901</v>
+        <v>0.4011557337406135</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2262,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>-2.817539083639132</v>
+        <v>-2.504479185457007</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2270,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1365499452234936</v>
+        <v>0.1384499452234936</v>
       </c>
       <c r="C11">
-        <v>72.72206343684671</v>
+        <v>69.65463484695773</v>
       </c>
       <c r="D11">
-        <v>78.62706343684671</v>
+        <v>77.01463484695773</v>
       </c>
       <c r="E11">
-        <v>-14.205</v>
+        <v>-12.75</v>
       </c>
       <c r="F11">
-        <v>13.095</v>
+        <v>14.55</v>
       </c>
       <c r="G11">
         <v>7.19</v>
@@ -2306,37 +2317,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M11">
-        <v>3.087801</v>
+        <v>3.43089</v>
       </c>
       <c r="N11">
-        <v>-10.82113433333333</v>
+        <v>-11.16422333333333</v>
       </c>
       <c r="O11">
-        <v>-3.029917613333333</v>
+        <v>-3.125982533333333</v>
       </c>
       <c r="P11">
-        <v>-7.791216719999997</v>
+        <v>-8.038240799999997</v>
       </c>
       <c r="Q11">
-        <v>19.60878328</v>
+        <v>19.3617592</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1103801419635587</v>
+        <v>0.1110976990964871</v>
       </c>
       <c r="T11">
-        <v>1.491458243962095</v>
+        <v>1.50803000222834</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>-0.701254171927962</v>
+        <v>-0.6311287547351658</v>
       </c>
       <c r="W11">
-        <v>0.4011557337406135</v>
+        <v>0.3846201603665521</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2344,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>-2.504479185457007</v>
+        <v>-2.254031266911306</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2352,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1384499452234936</v>
+        <v>0.1403499452234936</v>
       </c>
       <c r="C12">
-        <v>69.65463484695771</v>
+        <v>66.65201040504678</v>
       </c>
       <c r="D12">
-        <v>77.0146348469577</v>
+        <v>75.46701040504678</v>
       </c>
       <c r="E12">
-        <v>-12.75</v>
+        <v>-11.295</v>
       </c>
       <c r="F12">
-        <v>14.55</v>
+        <v>16.005</v>
       </c>
       <c r="G12">
         <v>7.19</v>
@@ -2388,37 +2399,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M12">
-        <v>3.43089</v>
+        <v>3.773979</v>
       </c>
       <c r="N12">
-        <v>-11.16422333333333</v>
+        <v>-11.50731233333333</v>
       </c>
       <c r="O12">
-        <v>-3.125982533333333</v>
+        <v>-3.222047453333333</v>
       </c>
       <c r="P12">
-        <v>-8.038240799999997</v>
+        <v>-8.285264879999998</v>
       </c>
       <c r="Q12">
-        <v>19.3617592</v>
+        <v>19.11473512</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1110976990964871</v>
+        <v>0.1118313811088072</v>
       </c>
       <c r="T12">
-        <v>1.50803000222834</v>
+        <v>1.524974159556748</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>-0.6311287547351657</v>
+        <v>-0.5737534133956053</v>
       </c>
       <c r="W12">
-        <v>0.3846201603665521</v>
+        <v>0.3710910548786837</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2426,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>-2.254031266911306</v>
+        <v>-2.049119333555733</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2434,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1403499452234936</v>
+        <v>0.1422499452234936</v>
       </c>
       <c r="C13">
-        <v>66.65201040504678</v>
+        <v>63.7103603148126</v>
       </c>
       <c r="D13">
-        <v>75.46701040504678</v>
+        <v>73.9803603148126</v>
       </c>
       <c r="E13">
-        <v>-11.295</v>
+        <v>-9.84</v>
       </c>
       <c r="F13">
-        <v>16.005</v>
+        <v>17.46</v>
       </c>
       <c r="G13">
         <v>7.19</v>
@@ -2470,37 +2481,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M13">
-        <v>3.773979</v>
+        <v>4.117068000000001</v>
       </c>
       <c r="N13">
-        <v>-11.50731233333333</v>
+        <v>-11.85040133333333</v>
       </c>
       <c r="O13">
-        <v>-3.222047453333333</v>
+        <v>-3.318112373333333</v>
       </c>
       <c r="P13">
-        <v>-8.285264879999998</v>
+        <v>-8.532288959999997</v>
       </c>
       <c r="Q13">
-        <v>19.11473512</v>
+        <v>18.86771104</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1118313811088072</v>
+        <v>0.1125817377123164</v>
       </c>
       <c r="T13">
-        <v>1.524974159556748</v>
+        <v>1.542303411369893</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>-0.5737534133956053</v>
+        <v>-0.5259406289459714</v>
       </c>
       <c r="W13">
-        <v>0.3710910548786837</v>
+        <v>0.35981680030546</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2508,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>-2.049119333555733</v>
+        <v>-1.878359389092755</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2516,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1422499452234936</v>
+        <v>0.1441499452234936</v>
       </c>
       <c r="C14">
-        <v>63.7103603148126</v>
+        <v>60.82615072777391</v>
       </c>
       <c r="D14">
-        <v>73.9803603148126</v>
+        <v>72.55115072777392</v>
       </c>
       <c r="E14">
-        <v>-9.84</v>
+        <v>-8.385000000000002</v>
       </c>
       <c r="F14">
-        <v>17.46</v>
+        <v>18.915</v>
       </c>
       <c r="G14">
         <v>7.19</v>
@@ -2552,37 +2563,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M14">
-        <v>4.117068000000001</v>
+        <v>4.460157</v>
       </c>
       <c r="N14">
-        <v>-11.85040133333333</v>
+        <v>-12.19349033333333</v>
       </c>
       <c r="O14">
-        <v>-3.318112373333333</v>
+        <v>-3.414177293333333</v>
       </c>
       <c r="P14">
-        <v>-8.532288959999997</v>
+        <v>-8.779313039999996</v>
       </c>
       <c r="Q14">
-        <v>18.86771104</v>
+        <v>18.62068696</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1125817377123164</v>
+        <v>0.1133493438929177</v>
       </c>
       <c r="T14">
-        <v>1.542303411369893</v>
+        <v>1.560031036787938</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>-0.5259406289459714</v>
+        <v>-0.4854836574885891</v>
       </c>
       <c r="W14">
-        <v>0.35981680030546</v>
+        <v>0.3502770464358093</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2590,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>-1.878359389092755</v>
+        <v>-1.733870205316389</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2598,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1441499452234936</v>
+        <v>0.1460499452234936</v>
       </c>
       <c r="C15">
-        <v>60.82615072777391</v>
+        <v>57.99611569832369</v>
       </c>
       <c r="D15">
-        <v>72.55115072777392</v>
+        <v>71.1761156983237</v>
       </c>
       <c r="E15">
-        <v>-8.385000000000002</v>
+        <v>-6.93</v>
       </c>
       <c r="F15">
-        <v>18.915</v>
+        <v>20.37</v>
       </c>
       <c r="G15">
         <v>7.19</v>
@@ -2634,37 +2645,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M15">
-        <v>4.460157</v>
+        <v>4.803246000000001</v>
       </c>
       <c r="N15">
-        <v>-12.19349033333333</v>
+        <v>-12.53657933333333</v>
       </c>
       <c r="O15">
-        <v>-3.414177293333333</v>
+        <v>-3.510242213333334</v>
       </c>
       <c r="P15">
-        <v>-8.779313039999996</v>
+        <v>-9.026337119999999</v>
       </c>
       <c r="Q15">
-        <v>18.62068696</v>
+        <v>18.37366288</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1133493438929177</v>
+        <v>0.1141348013800446</v>
       </c>
       <c r="T15">
-        <v>1.560031036787938</v>
+        <v>1.578170932564542</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>-0.4854836574885891</v>
+        <v>-0.4508062533822612</v>
       </c>
       <c r="W15">
-        <v>0.3502770464358093</v>
+        <v>0.3421001145475372</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2672,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>-1.733870205316389</v>
+        <v>-1.610022333508076</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2680,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1460499452234936</v>
+        <v>0.1479499452234936</v>
       </c>
       <c r="C16">
-        <v>57.99611569832369</v>
+        <v>55.21723226861714</v>
       </c>
       <c r="D16">
-        <v>71.1761156983237</v>
+        <v>69.85223226861714</v>
       </c>
       <c r="E16">
-        <v>-6.93</v>
+        <v>-5.474999999999998</v>
       </c>
       <c r="F16">
-        <v>20.37</v>
+        <v>21.825</v>
       </c>
       <c r="G16">
         <v>7.19</v>
@@ -2716,37 +2727,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M16">
-        <v>4.803246000000001</v>
+        <v>5.146335000000001</v>
       </c>
       <c r="N16">
-        <v>-12.53657933333333</v>
+        <v>-12.87966833333333</v>
       </c>
       <c r="O16">
-        <v>-3.510242213333334</v>
+        <v>-3.606307133333333</v>
       </c>
       <c r="P16">
-        <v>-9.026337119999999</v>
+        <v>-9.273361199999998</v>
       </c>
       <c r="Q16">
-        <v>18.37366288</v>
+        <v>18.1266388</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1141348013800446</v>
+        <v>0.1149387402198099</v>
       </c>
       <c r="T16">
-        <v>1.578170932564542</v>
+        <v>1.596737649418243</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>-0.4508062533822612</v>
+        <v>-0.4207525031567771</v>
       </c>
       <c r="W16">
-        <v>0.3421001145475372</v>
+        <v>0.3350134402443681</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2754,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>-1.610022333508076</v>
+        <v>-1.502687511274204</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2762,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1479499452234936</v>
+        <v>0.1498499452234936</v>
       </c>
       <c r="C17">
-        <v>55.21723226861714</v>
+        <v>52.48669828322871</v>
       </c>
       <c r="D17">
-        <v>69.85223226861714</v>
+        <v>68.57669828322871</v>
       </c>
       <c r="E17">
-        <v>-5.475000000000001</v>
+        <v>-4.02</v>
       </c>
       <c r="F17">
-        <v>21.825</v>
+        <v>23.28</v>
       </c>
       <c r="G17">
         <v>7.19</v>
@@ -2798,37 +2809,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M17">
-        <v>5.146335</v>
+        <v>5.489424000000001</v>
       </c>
       <c r="N17">
-        <v>-12.87966833333333</v>
+        <v>-13.22275733333333</v>
       </c>
       <c r="O17">
-        <v>-3.606307133333333</v>
+        <v>-3.702372053333333</v>
       </c>
       <c r="P17">
-        <v>-9.273361199999998</v>
+        <v>-9.520385279999998</v>
       </c>
       <c r="Q17">
-        <v>18.1266388</v>
+        <v>17.87961472</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1149387402198099</v>
+        <v>0.1157618204605219</v>
       </c>
       <c r="T17">
-        <v>1.596737649418242</v>
+        <v>1.615746430958936</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>-0.4207525031567772</v>
+        <v>-0.3944554717094785</v>
       </c>
       <c r="W17">
-        <v>0.3350134402443681</v>
+        <v>0.3288126002290951</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2836,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>-1.502687511274204</v>
+        <v>-1.408769541819566</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2844,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1498499452234936</v>
+        <v>0.1517499452234936</v>
       </c>
       <c r="C18">
-        <v>52.48669828322871</v>
+        <v>49.80191259090687</v>
       </c>
       <c r="D18">
-        <v>68.57669828322871</v>
+        <v>67.34691259090687</v>
       </c>
       <c r="E18">
-        <v>-4.02</v>
+        <v>-2.564999999999998</v>
       </c>
       <c r="F18">
-        <v>23.28</v>
+        <v>24.735</v>
       </c>
       <c r="G18">
         <v>7.19</v>
@@ -2880,37 +2891,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M18">
-        <v>5.489424000000001</v>
+        <v>5.832513000000001</v>
       </c>
       <c r="N18">
-        <v>-13.22275733333333</v>
+        <v>-13.56584633333333</v>
       </c>
       <c r="O18">
-        <v>-3.702372053333333</v>
+        <v>-3.798436973333333</v>
       </c>
       <c r="P18">
-        <v>-9.520385279999998</v>
+        <v>-9.767409359999998</v>
       </c>
       <c r="Q18">
-        <v>17.87961472</v>
+        <v>17.63259064</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1157618204605219</v>
+        <v>0.1166047339600463</v>
       </c>
       <c r="T18">
-        <v>1.615746430958936</v>
+        <v>1.635213255428321</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>-0.3944554717094785</v>
+        <v>-0.3712522086677446</v>
       </c>
       <c r="W18">
-        <v>0.3288126002290951</v>
+        <v>0.3233412708038542</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2918,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>-1.408769541819566</v>
+        <v>-1.325900745241944</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2926,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1517499452234936</v>
+        <v>0.1536499452234936</v>
       </c>
       <c r="C19">
-        <v>49.80191259090687</v>
+        <v>47.16045733905155</v>
       </c>
       <c r="D19">
-        <v>67.34691259090687</v>
+        <v>66.16045733905156</v>
       </c>
       <c r="E19">
-        <v>-2.564999999999998</v>
+        <v>-1.109999999999996</v>
       </c>
       <c r="F19">
-        <v>24.735</v>
+        <v>26.19</v>
       </c>
       <c r="G19">
         <v>7.19</v>
@@ -2962,37 +2973,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M19">
-        <v>5.832513000000001</v>
+        <v>6.175602000000001</v>
       </c>
       <c r="N19">
-        <v>-13.56584633333333</v>
+        <v>-13.90893533333333</v>
       </c>
       <c r="O19">
-        <v>-3.798436973333333</v>
+        <v>-3.894501893333334</v>
       </c>
       <c r="P19">
-        <v>-9.767409359999998</v>
+        <v>-10.01443344</v>
       </c>
       <c r="Q19">
-        <v>17.63259064</v>
+        <v>17.38556656</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1166047339600463</v>
+        <v>0.1174682063254127</v>
       </c>
       <c r="T19">
-        <v>1.635213255428321</v>
+        <v>1.65515488049452</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>-0.3712522086677446</v>
+        <v>-0.3506270859639809</v>
       </c>
       <c r="W19">
-        <v>0.3233412708038542</v>
+        <v>0.3184778668703067</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3000,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>-1.325900745241944</v>
+        <v>-1.252239592728503</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3008,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1536499452234936</v>
+        <v>0.1555499452234936</v>
       </c>
       <c r="C20">
-        <v>47.16045733905152</v>
+        <v>44.56008210730802</v>
       </c>
       <c r="D20">
-        <v>66.16045733905152</v>
+        <v>65.01508210730802</v>
       </c>
       <c r="E20">
-        <v>-1.110000000000003</v>
+        <v>0.3449999999999989</v>
       </c>
       <c r="F20">
-        <v>26.19</v>
+        <v>27.645</v>
       </c>
       <c r="G20">
         <v>7.19</v>
@@ -3044,37 +3055,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M20">
-        <v>6.175602</v>
+        <v>6.518691</v>
       </c>
       <c r="N20">
-        <v>-13.90893533333333</v>
+        <v>-14.25202433333333</v>
       </c>
       <c r="O20">
-        <v>-3.894501893333333</v>
+        <v>-3.990566813333333</v>
       </c>
       <c r="P20">
-        <v>-10.01443344</v>
+        <v>-10.26145752</v>
       </c>
       <c r="Q20">
-        <v>17.38556656</v>
+        <v>17.13854248</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1174682063254127</v>
+        <v>0.1183529989960968</v>
       </c>
       <c r="T20">
-        <v>1.65515488049452</v>
+        <v>1.675588891364822</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>-0.350627085963981</v>
+        <v>-0.3321730288079819</v>
       </c>
       <c r="W20">
-        <v>0.3184778668703068</v>
+        <v>0.3141264001929222</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3082,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>-1.252239592728503</v>
+        <v>-1.186332245742793</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3090,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1555499452234936</v>
+        <v>0.1574499452234936</v>
       </c>
       <c r="C21">
-        <v>44.56008210730802</v>
+        <v>41.99868966119788</v>
       </c>
       <c r="D21">
-        <v>65.01508210730802</v>
+        <v>63.90868966119788</v>
       </c>
       <c r="E21">
-        <v>0.3449999999999989</v>
+        <v>1.800000000000001</v>
       </c>
       <c r="F21">
-        <v>27.645</v>
+        <v>29.1</v>
       </c>
       <c r="G21">
         <v>7.19</v>
@@ -3126,37 +3137,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M21">
-        <v>6.518691</v>
+        <v>6.86178</v>
       </c>
       <c r="N21">
-        <v>-14.25202433333333</v>
+        <v>-14.59511333333333</v>
       </c>
       <c r="O21">
-        <v>-3.990566813333333</v>
+        <v>-4.086631733333333</v>
       </c>
       <c r="P21">
-        <v>-10.26145752</v>
+        <v>-10.5084816</v>
       </c>
       <c r="Q21">
-        <v>17.13854248</v>
+        <v>16.8915184</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1183529989960968</v>
+        <v>0.119259911483548</v>
       </c>
       <c r="T21">
-        <v>1.675588891364822</v>
+        <v>1.696533752506882</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>-0.3321730288079819</v>
+        <v>-0.3155643773675829</v>
       </c>
       <c r="W21">
-        <v>0.3141264001929222</v>
+        <v>0.3102100801832761</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3164,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>-1.186332245742793</v>
+        <v>-1.127015633455653</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3172,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1574499452234936</v>
+        <v>0.1593499452234936</v>
       </c>
       <c r="C22">
-        <v>41.99868966119788</v>
+        <v>39.47432313603328</v>
       </c>
       <c r="D22">
-        <v>63.90868966119788</v>
+        <v>62.83932313603329</v>
       </c>
       <c r="E22">
-        <v>1.800000000000001</v>
+        <v>3.255000000000003</v>
       </c>
       <c r="F22">
-        <v>29.1</v>
+        <v>30.555</v>
       </c>
       <c r="G22">
         <v>7.19</v>
@@ -3208,37 +3219,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M22">
-        <v>6.86178</v>
+        <v>7.204869000000001</v>
       </c>
       <c r="N22">
-        <v>-14.59511333333333</v>
+        <v>-14.93820233333333</v>
       </c>
       <c r="O22">
-        <v>-4.086631733333333</v>
+        <v>-4.182696653333333</v>
       </c>
       <c r="P22">
-        <v>-10.5084816</v>
+        <v>-10.75550568</v>
       </c>
       <c r="Q22">
-        <v>16.8915184</v>
+        <v>16.64449432</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.119259911483548</v>
+        <v>0.1201897837808081</v>
       </c>
       <c r="T22">
-        <v>1.696533752506882</v>
+        <v>1.718008863298109</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>-0.3155643773675829</v>
+        <v>-0.3005375022548408</v>
       </c>
       <c r="W22">
-        <v>0.3102100801832761</v>
+        <v>0.3066667430316914</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3246,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>-1.127015633455653</v>
+        <v>-1.073348222338717</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3254,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1593499452234936</v>
+        <v>0.1612499452234936</v>
       </c>
       <c r="C23">
-        <v>39.47432313603328</v>
+        <v>36.98515448634418</v>
       </c>
       <c r="D23">
-        <v>62.83932313603329</v>
+        <v>61.80515448634417</v>
       </c>
       <c r="E23">
-        <v>3.254999999999999</v>
+        <v>4.709999999999997</v>
       </c>
       <c r="F23">
-        <v>30.555</v>
+        <v>32.01</v>
       </c>
       <c r="G23">
         <v>7.19</v>
@@ -3290,37 +3301,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M23">
-        <v>7.204869</v>
+        <v>7.547958</v>
       </c>
       <c r="N23">
-        <v>-14.93820233333333</v>
+        <v>-15.28129133333333</v>
       </c>
       <c r="O23">
-        <v>-4.182696653333333</v>
+        <v>-4.278761573333333</v>
       </c>
       <c r="P23">
-        <v>-10.75550568</v>
+        <v>-11.00252976</v>
       </c>
       <c r="Q23">
-        <v>16.64449432</v>
+        <v>16.39747024</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1201897837808081</v>
+        <v>0.1211434989574851</v>
       </c>
       <c r="T23">
-        <v>1.718008863298109</v>
+        <v>1.740034617955777</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>-0.3005375022548408</v>
+        <v>-0.2868767066978026</v>
       </c>
       <c r="W23">
-        <v>0.3066667430316915</v>
+        <v>0.3034455274393419</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3328,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>-1.073348222338717</v>
+        <v>-1.024559666777866</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3336,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1612499452234936</v>
+        <v>0.1631499452234936</v>
       </c>
       <c r="C24">
-        <v>36.98515448634418</v>
+        <v>34.52947405738949</v>
       </c>
       <c r="D24">
-        <v>61.80515448634417</v>
+        <v>60.80447405738949</v>
       </c>
       <c r="E24">
-        <v>4.709999999999997</v>
+        <v>6.165000000000003</v>
       </c>
       <c r="F24">
-        <v>32.01</v>
+        <v>33.465</v>
       </c>
       <c r="G24">
         <v>7.19</v>
@@ -3372,37 +3383,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M24">
-        <v>7.547958</v>
+        <v>7.891047000000001</v>
       </c>
       <c r="N24">
-        <v>-15.28129133333333</v>
+        <v>-15.62438033333333</v>
       </c>
       <c r="O24">
-        <v>-4.278761573333333</v>
+        <v>-4.374826493333333</v>
       </c>
       <c r="P24">
-        <v>-11.00252976</v>
+        <v>-11.24955384</v>
       </c>
       <c r="Q24">
-        <v>16.39747024</v>
+        <v>16.15044616</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1211434989574851</v>
+        <v>0.122121985956933</v>
       </c>
       <c r="T24">
-        <v>1.740034617955777</v>
+        <v>1.762632470137021</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>-0.2868767066978026</v>
+        <v>-0.2744038064065938</v>
       </c>
       <c r="W24">
-        <v>0.3034455274393419</v>
+        <v>0.3005044175506749</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3410,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>-1.024559666777866</v>
+        <v>-0.9800135943092632</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3418,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1631499452234936</v>
+        <v>0.1650499452234936</v>
       </c>
       <c r="C25">
-        <v>34.52947405738949</v>
+        <v>32.10568115360644</v>
       </c>
       <c r="D25">
-        <v>60.80447405738949</v>
+        <v>59.83568115360644</v>
       </c>
       <c r="E25">
-        <v>6.165000000000003</v>
+        <v>7.620000000000001</v>
       </c>
       <c r="F25">
-        <v>33.465</v>
+        <v>34.92</v>
       </c>
       <c r="G25">
         <v>7.19</v>
@@ -3454,37 +3465,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M25">
-        <v>7.891047000000001</v>
+        <v>8.234136000000001</v>
       </c>
       <c r="N25">
-        <v>-15.62438033333333</v>
+        <v>-15.96746933333333</v>
       </c>
       <c r="O25">
-        <v>-4.374826493333333</v>
+        <v>-4.470891413333334</v>
       </c>
       <c r="P25">
-        <v>-11.24955384</v>
+        <v>-11.49657792</v>
       </c>
       <c r="Q25">
-        <v>16.15044616</v>
+        <v>15.90342208</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.122121985956933</v>
+        <v>0.123126222614261</v>
       </c>
       <c r="T25">
-        <v>1.762632470137021</v>
+        <v>1.785825002638824</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>-0.2744038064065938</v>
+        <v>-0.2629703144729857</v>
       </c>
       <c r="W25">
-        <v>0.3005044175506749</v>
+        <v>0.29780840015273</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3492,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>-0.9800135943092632</v>
+        <v>-0.9391796945463773</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3500,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1650499452234936</v>
+        <v>0.1669499452234936</v>
       </c>
       <c r="C26">
-        <v>32.10568115360644</v>
+        <v>29.71227549455206</v>
       </c>
       <c r="D26">
-        <v>59.83568115360644</v>
+        <v>58.89727549455206</v>
       </c>
       <c r="E26">
-        <v>7.620000000000001</v>
+        <v>9.074999999999999</v>
       </c>
       <c r="F26">
-        <v>34.92</v>
+        <v>36.375</v>
       </c>
       <c r="G26">
         <v>7.19</v>
@@ -3536,37 +3547,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M26">
-        <v>8.234136000000001</v>
+        <v>8.577225</v>
       </c>
       <c r="N26">
-        <v>-15.96746933333333</v>
+        <v>-16.31055833333333</v>
       </c>
       <c r="O26">
-        <v>-4.470891413333334</v>
+        <v>-4.566956333333334</v>
       </c>
       <c r="P26">
-        <v>-11.49657792</v>
+        <v>-11.743602</v>
       </c>
       <c r="Q26">
-        <v>15.90342208</v>
+        <v>15.656398</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.123126222614261</v>
+        <v>0.1241572389157845</v>
       </c>
       <c r="T26">
-        <v>1.785825002638824</v>
+        <v>1.809636002674008</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>-0.2629703144729857</v>
+        <v>-0.2524515018940663</v>
       </c>
       <c r="W26">
-        <v>0.29780840015273</v>
+        <v>0.2953280641466208</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3574,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>-0.9391796945463773</v>
+        <v>-0.9016125067645226</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3582,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1669499452234936</v>
+        <v>0.1688499452234936</v>
       </c>
       <c r="C27">
-        <v>29.71227549455206</v>
+        <v>27.34784946241204</v>
       </c>
       <c r="D27">
-        <v>58.89727549455206</v>
+        <v>57.98784946241204</v>
       </c>
       <c r="E27">
-        <v>9.074999999999999</v>
+        <v>10.53</v>
       </c>
       <c r="F27">
-        <v>36.375</v>
+        <v>37.83</v>
       </c>
       <c r="G27">
         <v>7.19</v>
@@ -3618,37 +3629,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M27">
-        <v>8.577225</v>
+        <v>8.920313999999999</v>
       </c>
       <c r="N27">
-        <v>-16.31055833333333</v>
+        <v>-16.65364733333333</v>
       </c>
       <c r="O27">
-        <v>-4.566956333333334</v>
+        <v>-4.663021253333334</v>
       </c>
       <c r="P27">
-        <v>-11.743602</v>
+        <v>-11.99062608</v>
       </c>
       <c r="Q27">
-        <v>15.656398</v>
+        <v>15.40937392</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1241572389157845</v>
+        <v>0.1252161205227546</v>
       </c>
       <c r="T27">
-        <v>1.809636002674008</v>
+        <v>1.834090543250684</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>-0.2524515018940663</v>
+        <v>-0.2427418287442945</v>
       </c>
       <c r="W27">
-        <v>0.2953280641466208</v>
+        <v>0.2930385232179047</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3656,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>-0.9016125067645226</v>
+        <v>-0.8669351026581948</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3664,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1688499452234936</v>
+        <v>0.1707499452234936</v>
       </c>
       <c r="C28">
-        <v>27.34784946241204</v>
+        <v>25.01108105681958</v>
       </c>
       <c r="D28">
-        <v>57.98784946241204</v>
+        <v>57.10608105681959</v>
       </c>
       <c r="E28">
-        <v>10.53</v>
+        <v>11.985</v>
       </c>
       <c r="F28">
-        <v>37.83</v>
+        <v>39.285</v>
       </c>
       <c r="G28">
         <v>7.19</v>
@@ -3700,37 +3711,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M28">
-        <v>8.920313999999999</v>
+        <v>9.263403000000002</v>
       </c>
       <c r="N28">
-        <v>-16.65364733333333</v>
+        <v>-16.99673633333333</v>
       </c>
       <c r="O28">
-        <v>-4.663021253333334</v>
+        <v>-4.759086173333333</v>
       </c>
       <c r="P28">
-        <v>-11.99062608</v>
+        <v>-12.23765016</v>
       </c>
       <c r="Q28">
-        <v>15.40937392</v>
+        <v>15.16234984</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1252161205227546</v>
+        <v>0.1263040125847101</v>
       </c>
       <c r="T28">
-        <v>1.834090543250684</v>
+        <v>1.859215071240419</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>-0.2427418287442945</v>
+        <v>-0.2337513906426539</v>
       </c>
       <c r="W28">
-        <v>0.2930385232179047</v>
+        <v>0.2909185779135378</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3738,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>-0.8669351026581948</v>
+        <v>-0.8348263951523351</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3746,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1707499452234936</v>
+        <v>0.1726499452234936</v>
       </c>
       <c r="C29">
-        <v>25.01108105681958</v>
+        <v>22.70072748282481</v>
       </c>
       <c r="D29">
-        <v>57.10608105681959</v>
+        <v>56.25072748282481</v>
       </c>
       <c r="E29">
-        <v>11.985</v>
+        <v>13.44</v>
       </c>
       <c r="F29">
-        <v>39.285</v>
+        <v>40.74</v>
       </c>
       <c r="G29">
         <v>7.19</v>
@@ -3782,37 +3793,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M29">
-        <v>9.263403000000002</v>
+        <v>9.606492000000001</v>
       </c>
       <c r="N29">
-        <v>-16.99673633333333</v>
+        <v>-17.33982533333333</v>
       </c>
       <c r="O29">
-        <v>-4.759086173333333</v>
+        <v>-4.855151093333333</v>
       </c>
       <c r="P29">
-        <v>-12.23765016</v>
+        <v>-12.48467424</v>
       </c>
       <c r="Q29">
-        <v>15.16234984</v>
+        <v>14.91532576</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1263040125847101</v>
+        <v>0.1274221238706089</v>
       </c>
       <c r="T29">
-        <v>1.859215071240419</v>
+        <v>1.885037502785425</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>-0.2337513906426539</v>
+        <v>-0.2254031266911306</v>
       </c>
       <c r="W29">
-        <v>0.2909185779135378</v>
+        <v>0.2889500572737686</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3820,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>-0.8348263951523351</v>
+        <v>-0.8050111667540376</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3828,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1726499452234936</v>
+        <v>0.1745499452234936</v>
       </c>
       <c r="C30">
-        <v>22.70072748282481</v>
+        <v>20.41561930660892</v>
       </c>
       <c r="D30">
-        <v>56.25072748282481</v>
+        <v>55.42061930660893</v>
       </c>
       <c r="E30">
-        <v>13.44</v>
+        <v>14.89500000000001</v>
       </c>
       <c r="F30">
-        <v>40.74</v>
+        <v>42.19500000000001</v>
       </c>
       <c r="G30">
         <v>7.19</v>
@@ -3864,37 +3875,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M30">
-        <v>9.606492000000001</v>
+        <v>9.949581000000002</v>
       </c>
       <c r="N30">
-        <v>-17.33982533333333</v>
+        <v>-17.68291433333333</v>
       </c>
       <c r="O30">
-        <v>-4.855151093333333</v>
+        <v>-4.951216013333334</v>
       </c>
       <c r="P30">
-        <v>-12.48467424</v>
+        <v>-12.73169832</v>
       </c>
       <c r="Q30">
-        <v>14.91532576</v>
+        <v>14.66830168</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1274221238706089</v>
+        <v>0.1285717312490682</v>
       </c>
       <c r="T30">
-        <v>1.885037502785425</v>
+        <v>1.911587326768319</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>-0.2254031266911306</v>
+        <v>-0.2176306050810916</v>
       </c>
       <c r="W30">
-        <v>0.2889500572737686</v>
+        <v>0.2871172966781214</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3902,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>-0.8050111667540376</v>
+        <v>-0.7772521610038985</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3910,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1745499452234936</v>
+        <v>0.1764499452234936</v>
       </c>
       <c r="C31">
-        <v>20.41561930660895</v>
+        <v>18.1546551211481</v>
       </c>
       <c r="D31">
-        <v>55.42061930660896</v>
+        <v>54.6146551211481</v>
       </c>
       <c r="E31">
-        <v>14.895</v>
+        <v>16.35</v>
       </c>
       <c r="F31">
-        <v>42.195</v>
+        <v>43.65</v>
       </c>
       <c r="G31">
         <v>7.19</v>
@@ -3946,37 +3957,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M31">
-        <v>9.949581</v>
+        <v>10.29267</v>
       </c>
       <c r="N31">
-        <v>-17.68291433333333</v>
+        <v>-18.02600333333333</v>
       </c>
       <c r="O31">
-        <v>-4.951216013333332</v>
+        <v>-5.047280933333332</v>
       </c>
       <c r="P31">
-        <v>-12.73169832</v>
+        <v>-12.9787224</v>
       </c>
       <c r="Q31">
-        <v>14.66830168</v>
+        <v>14.4212776</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1285717312490681</v>
+        <v>0.1297541845526263</v>
       </c>
       <c r="T31">
-        <v>1.911587326768318</v>
+        <v>1.938895717150723</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>-0.2176306050810916</v>
+        <v>-0.2103762515783886</v>
       </c>
       <c r="W31">
-        <v>0.2871172966781214</v>
+        <v>0.285406720122184</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3984,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>-0.7772521610038985</v>
+        <v>-0.7513437556371019</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3992,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1764499452234936</v>
+        <v>0.1783499452234936</v>
       </c>
       <c r="C32">
-        <v>18.1546551211481</v>
+        <v>15.91679667065825</v>
       </c>
       <c r="D32">
-        <v>54.6146551211481</v>
+        <v>53.83179667065825</v>
       </c>
       <c r="E32">
-        <v>16.35</v>
+        <v>17.805</v>
       </c>
       <c r="F32">
-        <v>43.65</v>
+        <v>45.105</v>
       </c>
       <c r="G32">
         <v>7.19</v>
@@ -4028,37 +4039,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M32">
-        <v>10.29267</v>
+        <v>10.635759</v>
       </c>
       <c r="N32">
-        <v>-18.02600333333333</v>
+        <v>-18.36909233333333</v>
       </c>
       <c r="O32">
-        <v>-5.047280933333332</v>
+        <v>-5.143345853333333</v>
       </c>
       <c r="P32">
-        <v>-12.9787224</v>
+        <v>-13.22574648</v>
       </c>
       <c r="Q32">
-        <v>14.4212776</v>
+        <v>14.17425352</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1297541845526263</v>
+        <v>0.1309709118649832</v>
       </c>
       <c r="T32">
-        <v>1.938895717150723</v>
+        <v>1.966995655080443</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>-0.2103762515783886</v>
+        <v>-0.2035899208823115</v>
       </c>
       <c r="W32">
-        <v>0.285406720122184</v>
+        <v>0.2838065033440491</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4066,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>-0.7513437556371019</v>
+        <v>-0.7271068602939696</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4074,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1783499452234936</v>
+        <v>0.1802499452234936</v>
       </c>
       <c r="C33">
-        <v>15.91679667065825</v>
+        <v>13.70106438843803</v>
       </c>
       <c r="D33">
-        <v>53.83179667065825</v>
+        <v>53.07106438843803</v>
       </c>
       <c r="E33">
-        <v>17.805</v>
+        <v>19.26</v>
       </c>
       <c r="F33">
-        <v>45.105</v>
+        <v>46.56</v>
       </c>
       <c r="G33">
         <v>7.19</v>
@@ -4110,37 +4121,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M33">
-        <v>10.635759</v>
+        <v>10.978848</v>
       </c>
       <c r="N33">
-        <v>-18.36909233333333</v>
+        <v>-18.71218133333333</v>
       </c>
       <c r="O33">
-        <v>-5.143345853333333</v>
+        <v>-5.239410773333334</v>
       </c>
       <c r="P33">
-        <v>-13.22574648</v>
+        <v>-13.47277056</v>
       </c>
       <c r="Q33">
-        <v>14.17425352</v>
+        <v>13.92722944</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1309709118649832</v>
+        <v>0.1322234252747623</v>
       </c>
       <c r="T33">
-        <v>1.966995655080443</v>
+        <v>1.995922061772803</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>-0.2035899208823115</v>
+        <v>-0.1972277358547393</v>
       </c>
       <c r="W33">
-        <v>0.2838065033440491</v>
+        <v>0.2823063001145475</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4148,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>-0.7271068602939696</v>
+        <v>-0.7043847709097832</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4156,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1802499452234936</v>
+        <v>0.1821499452234936</v>
       </c>
       <c r="C34">
-        <v>13.70106438843803</v>
+        <v>11.50653330778557</v>
       </c>
       <c r="D34">
-        <v>53.07106438843803</v>
+        <v>52.33153330778557</v>
       </c>
       <c r="E34">
-        <v>19.26</v>
+        <v>20.715</v>
       </c>
       <c r="F34">
-        <v>46.56</v>
+        <v>48.015</v>
       </c>
       <c r="G34">
         <v>7.19</v>
@@ -4192,37 +4203,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M34">
-        <v>10.978848</v>
+        <v>11.321937</v>
       </c>
       <c r="N34">
-        <v>-18.71218133333333</v>
+        <v>-19.05527033333333</v>
       </c>
       <c r="O34">
-        <v>-5.239410773333334</v>
+        <v>-5.335475693333334</v>
       </c>
       <c r="P34">
-        <v>-13.47277056</v>
+        <v>-13.71979464</v>
       </c>
       <c r="Q34">
-        <v>13.92722944</v>
+        <v>13.68020536</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1322234252747623</v>
+        <v>0.1335133271445349</v>
       </c>
       <c r="T34">
-        <v>1.995922061772803</v>
+        <v>2.0257119432918</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>-0.1972277358547393</v>
+        <v>-0.1912511377985351</v>
       </c>
       <c r="W34">
-        <v>0.2823063001145475</v>
+        <v>0.2808970182928946</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4230,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>-0.7043847709097832</v>
+        <v>-0.6830397778519111</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4238,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1821499452234936</v>
+        <v>0.1840499452234936</v>
       </c>
       <c r="C35">
-        <v>11.50653330778557</v>
+        <v>9.332329310098217</v>
       </c>
       <c r="D35">
-        <v>52.33153330778557</v>
+        <v>51.61232931009823</v>
       </c>
       <c r="E35">
-        <v>20.715</v>
+        <v>22.17000000000001</v>
       </c>
       <c r="F35">
-        <v>48.015</v>
+        <v>49.47000000000001</v>
       </c>
       <c r="G35">
         <v>7.19</v>
@@ -4274,37 +4285,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M35">
-        <v>11.321937</v>
+        <v>11.665026</v>
       </c>
       <c r="N35">
-        <v>-19.05527033333333</v>
+        <v>-19.39835933333333</v>
       </c>
       <c r="O35">
-        <v>-5.335475693333334</v>
+        <v>-5.431540613333333</v>
       </c>
       <c r="P35">
-        <v>-13.71979464</v>
+        <v>-13.96681872</v>
       </c>
       <c r="Q35">
-        <v>13.68020536</v>
+        <v>13.43318128</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1335133271445349</v>
+        <v>0.1348423169497552</v>
       </c>
       <c r="T35">
-        <v>2.0257119432918</v>
+        <v>2.056404548493191</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>-0.1912511377985351</v>
+        <v>-0.1856261043338723</v>
       </c>
       <c r="W35">
-        <v>0.2808970182928946</v>
+        <v>0.2795706354019271</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4312,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>-0.6830397778519111</v>
+        <v>-0.6629503726209722</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4320,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1840499452234936</v>
+        <v>0.1859499452234936</v>
       </c>
       <c r="C36">
-        <v>9.332329310098217</v>
+        <v>7.177625678157391</v>
       </c>
       <c r="D36">
-        <v>51.61232931009823</v>
+        <v>50.9126256781574</v>
       </c>
       <c r="E36">
-        <v>22.17000000000001</v>
+        <v>23.625</v>
       </c>
       <c r="F36">
-        <v>49.47000000000001</v>
+        <v>50.925</v>
       </c>
       <c r="G36">
         <v>7.19</v>
@@ -4356,37 +4367,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M36">
-        <v>11.665026</v>
+        <v>12.008115</v>
       </c>
       <c r="N36">
-        <v>-19.39835933333333</v>
+        <v>-19.74144833333333</v>
       </c>
       <c r="O36">
-        <v>-5.431540613333333</v>
+        <v>-5.527605533333333</v>
       </c>
       <c r="P36">
-        <v>-13.96681872</v>
+        <v>-14.2138428</v>
       </c>
       <c r="Q36">
-        <v>13.43318128</v>
+        <v>13.1861572</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1348423169497552</v>
+        <v>0.1362121987489822</v>
       </c>
       <c r="T36">
-        <v>2.056404548493191</v>
+        <v>2.088041541546933</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>-0.1856261043338723</v>
+        <v>-0.1803225013529045</v>
       </c>
       <c r="W36">
-        <v>0.2795706354019271</v>
+        <v>0.2783200458190149</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4394,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>-0.6629503726209722</v>
+        <v>-0.64400893340323</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4402,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1859499452234936</v>
+        <v>0.1878499452234936</v>
       </c>
       <c r="C37">
-        <v>7.177625678157391</v>
+        <v>5.041639926024196</v>
       </c>
       <c r="D37">
-        <v>50.9126256781574</v>
+        <v>50.23163992602421</v>
       </c>
       <c r="E37">
-        <v>23.625</v>
+        <v>25.08000000000001</v>
       </c>
       <c r="F37">
-        <v>50.925</v>
+        <v>52.38000000000001</v>
       </c>
       <c r="G37">
         <v>7.19</v>
@@ -4438,37 +4449,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M37">
-        <v>12.008115</v>
+        <v>12.351204</v>
       </c>
       <c r="N37">
-        <v>-19.74144833333333</v>
+        <v>-20.08453733333333</v>
       </c>
       <c r="O37">
-        <v>-5.527605533333333</v>
+        <v>-5.623670453333334</v>
       </c>
       <c r="P37">
-        <v>-14.2138428</v>
+        <v>-14.46086688</v>
       </c>
       <c r="Q37">
-        <v>13.1861572</v>
+        <v>12.93913312</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1362121987489822</v>
+        <v>0.137624889354435</v>
       </c>
       <c r="T37">
-        <v>2.088041541546933</v>
+        <v>2.120667190633603</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>-0.1803225013529045</v>
+        <v>-0.1753135429819905</v>
       </c>
       <c r="W37">
-        <v>0.2783200458190149</v>
+        <v>0.2771389334351534</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4476,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>-0.64400893340323</v>
+        <v>-0.6261197963642515</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4484,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1878499452234936</v>
+        <v>0.1897499452234936</v>
       </c>
       <c r="C38">
-        <v>5.04163992602421</v>
+        <v>2.923630879989034</v>
       </c>
       <c r="D38">
-        <v>50.23163992602421</v>
+        <v>49.56863087998904</v>
       </c>
       <c r="E38">
-        <v>25.07999999999999</v>
+        <v>26.535</v>
       </c>
       <c r="F38">
-        <v>52.38</v>
+        <v>53.835</v>
       </c>
       <c r="G38">
         <v>7.19</v>
@@ -4520,37 +4531,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M38">
-        <v>12.351204</v>
+        <v>12.694293</v>
       </c>
       <c r="N38">
-        <v>-20.08453733333333</v>
+        <v>-20.42762633333333</v>
       </c>
       <c r="O38">
-        <v>-5.623670453333333</v>
+        <v>-5.719735373333332</v>
       </c>
       <c r="P38">
-        <v>-14.46086688</v>
+        <v>-14.70789096</v>
       </c>
       <c r="Q38">
-        <v>12.93913312</v>
+        <v>12.69210904</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.137624889354435</v>
+        <v>0.1390824272806959</v>
       </c>
       <c r="T38">
-        <v>2.120667190633603</v>
+        <v>2.154328574611915</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>-0.1753135429819905</v>
+        <v>-0.1705753391176124</v>
       </c>
       <c r="W38">
-        <v>0.2771389334351534</v>
+        <v>0.276021664963933</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4558,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>-0.6261197963642517</v>
+        <v>-0.6091976397057584</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4566,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1897499452234936</v>
+        <v>0.1916499452234936</v>
       </c>
       <c r="C39">
-        <v>2.923630879989034</v>
+        <v>0.8228959876813136</v>
       </c>
       <c r="D39">
-        <v>49.56863087998904</v>
+        <v>48.92289598768131</v>
       </c>
       <c r="E39">
-        <v>26.535</v>
+        <v>27.99</v>
       </c>
       <c r="F39">
-        <v>53.835</v>
+        <v>55.29</v>
       </c>
       <c r="G39">
         <v>7.19</v>
@@ -4602,37 +4613,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M39">
-        <v>12.694293</v>
+        <v>13.037382</v>
       </c>
       <c r="N39">
-        <v>-20.42762633333333</v>
+        <v>-20.77071533333333</v>
       </c>
       <c r="O39">
-        <v>-5.719735373333332</v>
+        <v>-5.815800293333333</v>
       </c>
       <c r="P39">
-        <v>-14.70789096</v>
+        <v>-14.95491504</v>
       </c>
       <c r="Q39">
-        <v>12.69210904</v>
+        <v>12.44508496</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1390824272806959</v>
+        <v>0.1405869825594168</v>
       </c>
       <c r="T39">
-        <v>2.154328574611915</v>
+        <v>2.1890758096863</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>-0.1705753391176124</v>
+        <v>-0.166086514403991</v>
       </c>
       <c r="W39">
-        <v>0.276021664963933</v>
+        <v>0.2749632000964611</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4640,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>-0.6091976397057584</v>
+        <v>-0.5931661228713963</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4648,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1916499452234936</v>
+        <v>0.1935499452234936</v>
       </c>
       <c r="C40">
-        <v>0.8228959876813136</v>
+        <v>-1.261231165198446</v>
       </c>
       <c r="D40">
-        <v>48.92289598768131</v>
+        <v>48.29376883480156</v>
       </c>
       <c r="E40">
-        <v>27.99</v>
+        <v>29.445</v>
       </c>
       <c r="F40">
-        <v>55.29</v>
+        <v>56.745</v>
       </c>
       <c r="G40">
         <v>7.19</v>
@@ -4684,37 +4695,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M40">
-        <v>13.037382</v>
+        <v>13.380471</v>
       </c>
       <c r="N40">
-        <v>-20.77071533333333</v>
+        <v>-21.11380433333333</v>
       </c>
       <c r="O40">
-        <v>-5.815800293333333</v>
+        <v>-5.911865213333334</v>
       </c>
       <c r="P40">
-        <v>-14.95491504</v>
+        <v>-15.20193912</v>
       </c>
       <c r="Q40">
-        <v>12.44508496</v>
+        <v>12.19806088</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1405869825594168</v>
+        <v>0.1421408675194072</v>
       </c>
       <c r="T40">
-        <v>2.1890758096863</v>
+        <v>2.224962298369682</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>-0.166086514403991</v>
+        <v>-0.1618278858295296</v>
       </c>
       <c r="W40">
-        <v>0.2749632000964611</v>
+        <v>0.2739590154786031</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4722,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>-0.5931661228713963</v>
+        <v>-0.5779567351054631</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4730,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1935499452234936</v>
+        <v>0.1954499452234936</v>
       </c>
       <c r="C41">
-        <v>-1.261231165198446</v>
+        <v>-3.329383148976881</v>
       </c>
       <c r="D41">
-        <v>48.29376883480156</v>
+        <v>47.68061685102312</v>
       </c>
       <c r="E41">
-        <v>29.445</v>
+        <v>30.9</v>
       </c>
       <c r="F41">
-        <v>56.745</v>
+        <v>58.2</v>
       </c>
       <c r="G41">
         <v>7.19</v>
@@ -4766,37 +4777,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M41">
-        <v>13.380471</v>
+        <v>13.72356</v>
       </c>
       <c r="N41">
-        <v>-21.11380433333333</v>
+        <v>-21.45689333333333</v>
       </c>
       <c r="O41">
-        <v>-5.911865213333334</v>
+        <v>-6.007930133333334</v>
       </c>
       <c r="P41">
-        <v>-15.20193912</v>
+        <v>-15.4489632</v>
       </c>
       <c r="Q41">
-        <v>12.19806088</v>
+        <v>11.9510368</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1421408675194072</v>
+        <v>0.1437465486447306</v>
       </c>
       <c r="T41">
-        <v>2.224962298369682</v>
+        <v>2.26204500334251</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>-0.1618278858295296</v>
+        <v>-0.1577821886837914</v>
       </c>
       <c r="W41">
-        <v>0.2739590154786031</v>
+        <v>0.273005040091638</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4804,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>-0.5779567351054631</v>
+        <v>-0.5635078167278267</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4812,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1954499452234936</v>
+        <v>0.1973499452234936</v>
       </c>
       <c r="C42">
-        <v>-3.329383148976881</v>
+        <v>-5.382160811537879</v>
       </c>
       <c r="D42">
-        <v>47.68061685102312</v>
+        <v>47.08283918846212</v>
       </c>
       <c r="E42">
-        <v>30.9</v>
+        <v>32.355</v>
       </c>
       <c r="F42">
-        <v>58.2</v>
+        <v>59.655</v>
       </c>
       <c r="G42">
         <v>7.19</v>
@@ -4848,37 +4859,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M42">
-        <v>13.72356</v>
+        <v>14.066649</v>
       </c>
       <c r="N42">
-        <v>-21.45689333333333</v>
+        <v>-21.79998233333333</v>
       </c>
       <c r="O42">
-        <v>-6.007930133333334</v>
+        <v>-6.103995053333334</v>
       </c>
       <c r="P42">
-        <v>-15.4489632</v>
+        <v>-15.69598728</v>
       </c>
       <c r="Q42">
-        <v>11.9510368</v>
+        <v>11.70401272</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1437465486447306</v>
+        <v>0.1454066596387091</v>
       </c>
       <c r="T42">
-        <v>2.26204500334251</v>
+        <v>2.300384749161875</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>-0.1577821886837914</v>
+        <v>-0.1539338426183331</v>
       </c>
       <c r="W42">
-        <v>0.273005040091638</v>
+        <v>0.272097600089403</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4886,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>-0.5635078167278267</v>
+        <v>-0.549763723636904</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4894,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1973499452234936</v>
+        <v>0.1992499452234936</v>
       </c>
       <c r="C43">
-        <v>-5.382160811537879</v>
+        <v>-7.42013524224091</v>
       </c>
       <c r="D43">
-        <v>47.08283918846212</v>
+        <v>46.4998647577591</v>
       </c>
       <c r="E43">
-        <v>32.355</v>
+        <v>33.81</v>
       </c>
       <c r="F43">
-        <v>59.655</v>
+        <v>61.11000000000001</v>
       </c>
       <c r="G43">
         <v>7.19</v>
@@ -4930,37 +4941,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M43">
-        <v>14.066649</v>
+        <v>14.409738</v>
       </c>
       <c r="N43">
-        <v>-21.79998233333333</v>
+        <v>-22.14307133333333</v>
       </c>
       <c r="O43">
-        <v>-6.103995053333334</v>
+        <v>-6.200059973333333</v>
       </c>
       <c r="P43">
-        <v>-15.69598728</v>
+        <v>-15.94301136</v>
       </c>
       <c r="Q43">
-        <v>11.70401272</v>
+        <v>11.45698864</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1454066596387091</v>
+        <v>0.1471240158393765</v>
       </c>
       <c r="T43">
-        <v>2.300384749161875</v>
+        <v>2.340046555181907</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>-0.1539338426183331</v>
+        <v>-0.1502687511274204</v>
       </c>
       <c r="W43">
-        <v>0.272097600089403</v>
+        <v>0.2712333715158457</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4968,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>-0.549763723636904</v>
+        <v>-0.5366741111693583</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4976,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1992499452234936</v>
+        <v>0.2011499452234936</v>
       </c>
       <c r="C44">
-        <v>-7.420135242240903</v>
+        <v>-9.443849591722255</v>
       </c>
       <c r="D44">
-        <v>46.4998647577591</v>
+        <v>45.93115040827774</v>
       </c>
       <c r="E44">
-        <v>33.81</v>
+        <v>35.265</v>
       </c>
       <c r="F44">
-        <v>61.11</v>
+        <v>62.565</v>
       </c>
       <c r="G44">
         <v>7.19</v>
@@ -5012,37 +5023,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M44">
-        <v>14.409738</v>
+        <v>14.752827</v>
       </c>
       <c r="N44">
-        <v>-22.14307133333333</v>
+        <v>-22.48616033333333</v>
       </c>
       <c r="O44">
-        <v>-6.200059973333333</v>
+        <v>-6.296124893333333</v>
       </c>
       <c r="P44">
-        <v>-15.94301136</v>
+        <v>-16.19003544</v>
       </c>
       <c r="Q44">
-        <v>11.45698864</v>
+        <v>11.20996456</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1471240158393765</v>
+        <v>0.148901630152348</v>
       </c>
       <c r="T44">
-        <v>2.340046555181907</v>
+        <v>2.381100003518431</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>-0.1502687511274204</v>
+        <v>-0.1467741290081781</v>
       </c>
       <c r="W44">
-        <v>0.2712333715158457</v>
+        <v>0.2704093396201284</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5050,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>-0.5366741111693585</v>
+        <v>-0.5241933178863503</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5058,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2011499452234936</v>
+        <v>0.2030499452234936</v>
       </c>
       <c r="C45">
-        <v>-9.443849591722255</v>
+        <v>-11.45382075976747</v>
       </c>
       <c r="D45">
-        <v>45.93115040827774</v>
+        <v>45.37617924023253</v>
       </c>
       <c r="E45">
-        <v>35.265</v>
+        <v>36.72</v>
       </c>
       <c r="F45">
-        <v>62.565</v>
+        <v>64.02</v>
       </c>
       <c r="G45">
         <v>7.19</v>
@@ -5094,37 +5105,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M45">
-        <v>14.752827</v>
+        <v>15.095916</v>
       </c>
       <c r="N45">
-        <v>-22.48616033333333</v>
+        <v>-22.82924933333333</v>
       </c>
       <c r="O45">
-        <v>-6.296124893333333</v>
+        <v>-6.392189813333333</v>
       </c>
       <c r="P45">
-        <v>-16.19003544</v>
+        <v>-16.43705952</v>
       </c>
       <c r="Q45">
-        <v>11.20996456</v>
+        <v>10.96294048</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.148901630152348</v>
+        <v>0.1507427306907828</v>
       </c>
       <c r="T45">
-        <v>2.381100003518431</v>
+        <v>2.423619646438404</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>-0.1467741290081781</v>
+        <v>-0.1434383533489013</v>
       </c>
       <c r="W45">
-        <v>0.2704093396201284</v>
+        <v>0.269622763719671</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5132,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>-0.5241933178863503</v>
+        <v>-0.5122798333889331</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5140,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2030499452234936</v>
+        <v>0.2049499452234936</v>
       </c>
       <c r="C46">
-        <v>-11.45382075976747</v>
+        <v>-13.45054096228071</v>
       </c>
       <c r="D46">
-        <v>45.37617924023253</v>
+        <v>44.8344590377193</v>
       </c>
       <c r="E46">
-        <v>36.72</v>
+        <v>38.17500000000001</v>
       </c>
       <c r="F46">
-        <v>64.02</v>
+        <v>65.47500000000001</v>
       </c>
       <c r="G46">
         <v>7.19</v>
@@ -5176,37 +5187,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M46">
-        <v>15.095916</v>
+        <v>15.439005</v>
       </c>
       <c r="N46">
-        <v>-22.82924933333333</v>
+        <v>-23.17233833333334</v>
       </c>
       <c r="O46">
-        <v>-6.392189813333333</v>
+        <v>-6.488254733333335</v>
       </c>
       <c r="P46">
-        <v>-16.43705952</v>
+        <v>-16.6840836</v>
       </c>
       <c r="Q46">
-        <v>10.96294048</v>
+        <v>10.7159164</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1507427306907828</v>
+        <v>0.1526507803397061</v>
       </c>
       <c r="T46">
-        <v>2.423619646438404</v>
+        <v>2.467685458191829</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>-0.1434383533489013</v>
+        <v>-0.1402508343855924</v>
       </c>
       <c r="W46">
-        <v>0.269622763719671</v>
+        <v>0.2688711467481227</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5214,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>-0.5122798333889331</v>
+        <v>-0.5008958370914014</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5222,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2049499452234936</v>
+        <v>0.2068499452234936</v>
       </c>
       <c r="C47">
-        <v>-13.45054096228071</v>
+        <v>-15.43447918733538</v>
       </c>
       <c r="D47">
-        <v>44.8344590377193</v>
+        <v>44.30552081266463</v>
       </c>
       <c r="E47">
-        <v>38.17500000000001</v>
+        <v>39.63000000000001</v>
       </c>
       <c r="F47">
-        <v>65.47500000000001</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="G47">
         <v>7.19</v>
@@ -5258,37 +5269,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M47">
-        <v>15.439005</v>
+        <v>15.782094</v>
       </c>
       <c r="N47">
-        <v>-23.17233833333334</v>
+        <v>-23.51542733333334</v>
       </c>
       <c r="O47">
-        <v>-6.488254733333335</v>
+        <v>-6.584319653333335</v>
       </c>
       <c r="P47">
-        <v>-16.6840836</v>
+        <v>-16.93110768</v>
       </c>
       <c r="Q47">
-        <v>10.7159164</v>
+        <v>10.46889232</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1526507803397061</v>
+        <v>0.1546294984941452</v>
       </c>
       <c r="T47">
-        <v>2.467685458191829</v>
+        <v>2.513383337047233</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>-0.1402508343855924</v>
+        <v>-0.1372019032032969</v>
       </c>
       <c r="W47">
-        <v>0.2688711467481227</v>
+        <v>0.2681522087753374</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5296,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>-0.5008958370914014</v>
+        <v>-0.4900067971546318</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5304,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2068499452234936</v>
+        <v>0.2087499452234936</v>
       </c>
       <c r="C48">
-        <v>-15.43447918733538</v>
+        <v>-17.40608254935925</v>
       </c>
       <c r="D48">
-        <v>44.30552081266463</v>
+        <v>43.78891745064076</v>
       </c>
       <c r="E48">
-        <v>39.63000000000001</v>
+        <v>41.08500000000001</v>
       </c>
       <c r="F48">
-        <v>66.93000000000001</v>
+        <v>68.38500000000001</v>
       </c>
       <c r="G48">
         <v>7.19</v>
@@ -5340,37 +5351,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M48">
-        <v>15.782094</v>
+        <v>16.125183</v>
       </c>
       <c r="N48">
-        <v>-23.51542733333334</v>
+        <v>-23.85851633333333</v>
       </c>
       <c r="O48">
-        <v>-6.584319653333335</v>
+        <v>-6.680384573333334</v>
       </c>
       <c r="P48">
-        <v>-16.93110768</v>
+        <v>-17.17813176</v>
       </c>
       <c r="Q48">
-        <v>10.46889232</v>
+        <v>10.22186824</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1546294984941452</v>
+        <v>0.1566828852581856</v>
       </c>
       <c r="T48">
-        <v>2.513383337047233</v>
+        <v>2.560805664161332</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>-0.1372019032032969</v>
+        <v>-0.1342827137734395</v>
       </c>
       <c r="W48">
-        <v>0.2681522087753374</v>
+        <v>0.267463863907777</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5378,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>-0.4900067971546318</v>
+        <v>-0.4795811206194267</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5386,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2087499452234936</v>
+        <v>0.2106499452234936</v>
       </c>
       <c r="C49">
-        <v>-17.40608254935925</v>
+        <v>-19.36577754967254</v>
       </c>
       <c r="D49">
-        <v>43.78891745064076</v>
+        <v>43.28422245032747</v>
       </c>
       <c r="E49">
-        <v>41.08500000000001</v>
+        <v>42.54000000000001</v>
       </c>
       <c r="F49">
-        <v>68.38500000000001</v>
+        <v>69.84</v>
       </c>
       <c r="G49">
         <v>7.19</v>
@@ -5422,37 +5433,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M49">
-        <v>16.125183</v>
+        <v>16.468272</v>
       </c>
       <c r="N49">
-        <v>-23.85851633333333</v>
+        <v>-24.20160533333333</v>
       </c>
       <c r="O49">
-        <v>-6.680384573333334</v>
+        <v>-6.776449493333334</v>
       </c>
       <c r="P49">
-        <v>-17.17813176</v>
+        <v>-17.42515584</v>
       </c>
       <c r="Q49">
-        <v>10.22186824</v>
+        <v>9.97484416</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1566828852581856</v>
+        <v>0.1588152484362277</v>
       </c>
       <c r="T49">
-        <v>2.560805664161332</v>
+        <v>2.610051926933665</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>-0.1342827137734395</v>
+        <v>-0.1314851572364928</v>
       </c>
       <c r="W49">
-        <v>0.267463863907777</v>
+        <v>0.266804200076365</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5460,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>-0.4795811206194267</v>
+        <v>-0.4695898472731888</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5468,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2106499452234936</v>
+        <v>0.2125499452234936</v>
       </c>
       <c r="C50">
-        <v>-19.36577754967254</v>
+        <v>-21.31397125084825</v>
       </c>
       <c r="D50">
-        <v>43.28422245032747</v>
+        <v>42.79102874915176</v>
       </c>
       <c r="E50">
-        <v>42.54000000000001</v>
+        <v>43.995</v>
       </c>
       <c r="F50">
-        <v>69.84</v>
+        <v>71.295</v>
       </c>
       <c r="G50">
         <v>7.19</v>
@@ -5504,37 +5515,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M50">
-        <v>16.468272</v>
+        <v>16.811361</v>
       </c>
       <c r="N50">
-        <v>-24.20160533333333</v>
+        <v>-24.54469433333333</v>
       </c>
       <c r="O50">
-        <v>-6.776449493333334</v>
+        <v>-6.872514413333334</v>
       </c>
       <c r="P50">
-        <v>-17.42515584</v>
+        <v>-17.67217992</v>
       </c>
       <c r="Q50">
-        <v>9.97484416</v>
+        <v>9.727820080000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1588152484362277</v>
+        <v>0.1610312336996831</v>
       </c>
       <c r="T50">
-        <v>2.610051926933665</v>
+        <v>2.661229415697071</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>-0.1314851572364928</v>
+        <v>-0.128801786680646</v>
       </c>
       <c r="W50">
-        <v>0.266804200076365</v>
+        <v>0.2661714612992964</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5542,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>-0.4695898472731888</v>
+        <v>-0.4600063810023074</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5550,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2125499452234936</v>
+        <v>0.2144499452234936</v>
       </c>
       <c r="C51">
-        <v>-21.31397125084825</v>
+        <v>-23.25105237169088</v>
       </c>
       <c r="D51">
-        <v>42.79102874915176</v>
+        <v>42.30894762830913</v>
       </c>
       <c r="E51">
-        <v>43.995</v>
+        <v>45.45</v>
       </c>
       <c r="F51">
-        <v>71.295</v>
+        <v>72.75</v>
       </c>
       <c r="G51">
         <v>7.19</v>
@@ -5586,37 +5597,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M51">
-        <v>16.811361</v>
+        <v>17.15445</v>
       </c>
       <c r="N51">
-        <v>-24.54469433333333</v>
+        <v>-24.88778333333333</v>
       </c>
       <c r="O51">
-        <v>-6.872514413333334</v>
+        <v>-6.968579333333333</v>
       </c>
       <c r="P51">
-        <v>-17.67217992</v>
+        <v>-17.919204</v>
       </c>
       <c r="Q51">
-        <v>9.727820080000001</v>
+        <v>9.480796000000002</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1610312336996831</v>
+        <v>0.1633358583736768</v>
       </c>
       <c r="T51">
-        <v>2.661229415697071</v>
+        <v>2.714454004011012</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>-0.128801786680646</v>
+        <v>-0.1262257509470331</v>
       </c>
       <c r="W51">
-        <v>0.2661714612992964</v>
+        <v>0.2655640320733105</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5624,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>-0.4600063810023074</v>
+        <v>-0.4508062533822612</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5632,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2144499452234936</v>
+        <v>0.2163499452234936</v>
       </c>
       <c r="C52">
-        <v>-23.25105237169088</v>
+        <v>-25.17739230902387</v>
       </c>
       <c r="D52">
-        <v>42.30894762830913</v>
+        <v>41.83760769097613</v>
       </c>
       <c r="E52">
-        <v>45.45</v>
+        <v>46.905</v>
       </c>
       <c r="F52">
-        <v>72.75</v>
+        <v>74.205</v>
       </c>
       <c r="G52">
         <v>7.19</v>
@@ -5668,37 +5679,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M52">
-        <v>17.15445</v>
+        <v>17.497539</v>
       </c>
       <c r="N52">
-        <v>-24.88778333333333</v>
+        <v>-25.23087233333333</v>
       </c>
       <c r="O52">
-        <v>-6.968579333333333</v>
+        <v>-7.064644253333333</v>
       </c>
       <c r="P52">
-        <v>-17.919204</v>
+        <v>-18.16622808</v>
       </c>
       <c r="Q52">
-        <v>9.480796000000002</v>
+        <v>9.233771920000002</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1633358583736768</v>
+        <v>0.1657345493608947</v>
       </c>
       <c r="T52">
-        <v>2.714454004011012</v>
+        <v>2.769851024501033</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>-0.1262257509470331</v>
+        <v>-0.1237507362225815</v>
       </c>
       <c r="W52">
-        <v>0.2655640320733105</v>
+        <v>0.2649804236012848</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5706,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>-0.4508062533822612</v>
+        <v>-0.4419669150806482</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5714,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2163499452234936</v>
+        <v>0.2182499452234936</v>
       </c>
       <c r="C53">
-        <v>-25.17739230902387</v>
+        <v>-27.09334609193075</v>
       </c>
       <c r="D53">
-        <v>41.83760769097613</v>
+        <v>41.37665390806924</v>
       </c>
       <c r="E53">
-        <v>46.905</v>
+        <v>48.36</v>
       </c>
       <c r="F53">
-        <v>74.205</v>
+        <v>75.66</v>
       </c>
       <c r="G53">
         <v>7.19</v>
@@ -5750,37 +5761,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M53">
-        <v>17.497539</v>
+        <v>17.840628</v>
       </c>
       <c r="N53">
-        <v>-25.23087233333333</v>
+        <v>-25.57396133333333</v>
       </c>
       <c r="O53">
-        <v>-7.064644253333333</v>
+        <v>-7.160709173333333</v>
       </c>
       <c r="P53">
-        <v>-18.16622808</v>
+        <v>-18.41325216</v>
       </c>
       <c r="Q53">
-        <v>9.233771920000002</v>
+        <v>8.986747840000003</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1657345493608947</v>
+        <v>0.1682331858059133</v>
       </c>
       <c r="T53">
-        <v>2.769851024501033</v>
+        <v>2.827556254178138</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>-0.1237507362225815</v>
+        <v>-0.1213709143721473</v>
       </c>
       <c r="W53">
-        <v>0.2649804236012848</v>
+        <v>0.2644192616089523</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5788,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>-0.4419669150806482</v>
+        <v>-0.4334675513290973</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5796,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2182499452234936</v>
+        <v>0.2201499452234936</v>
       </c>
       <c r="C54">
-        <v>-27.09334609193075</v>
+        <v>-28.99925327360241</v>
       </c>
       <c r="D54">
-        <v>41.37665390806924</v>
+        <v>40.9257467263976</v>
       </c>
       <c r="E54">
-        <v>48.36</v>
+        <v>49.81500000000001</v>
       </c>
       <c r="F54">
-        <v>75.66</v>
+        <v>77.11500000000001</v>
       </c>
       <c r="G54">
         <v>7.19</v>
@@ -5832,37 +5843,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M54">
-        <v>17.840628</v>
+        <v>18.183717</v>
       </c>
       <c r="N54">
-        <v>-25.57396133333333</v>
+        <v>-25.91705033333333</v>
       </c>
       <c r="O54">
-        <v>-7.160709173333333</v>
+        <v>-7.256774093333334</v>
       </c>
       <c r="P54">
-        <v>-18.41325216</v>
+        <v>-18.66027624</v>
       </c>
       <c r="Q54">
-        <v>8.986747840000003</v>
+        <v>8.73972376</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1682331858059133</v>
+        <v>0.1708381472060392</v>
       </c>
       <c r="T54">
-        <v>2.827556254178138</v>
+        <v>2.88771702554363</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>-0.1213709143721473</v>
+        <v>-0.1190808971198426</v>
       </c>
       <c r="W54">
-        <v>0.2644192616089523</v>
+        <v>0.2638792755408589</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5870,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>-0.4334675513290973</v>
+        <v>-0.425288918285152</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5878,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2201499452234936</v>
+        <v>0.2220499452234936</v>
       </c>
       <c r="C55">
-        <v>-28.99925327360241</v>
+        <v>-30.8954387654989</v>
       </c>
       <c r="D55">
-        <v>40.9257467263976</v>
+        <v>40.48456123450111</v>
       </c>
       <c r="E55">
-        <v>49.81500000000001</v>
+        <v>51.27000000000001</v>
       </c>
       <c r="F55">
-        <v>77.11500000000001</v>
+        <v>78.57000000000001</v>
       </c>
       <c r="G55">
         <v>7.19</v>
@@ -5914,37 +5925,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M55">
-        <v>18.183717</v>
+        <v>18.526806</v>
       </c>
       <c r="N55">
-        <v>-25.91705033333333</v>
+        <v>-26.26013933333333</v>
       </c>
       <c r="O55">
-        <v>-7.256774093333334</v>
+        <v>-7.352839013333335</v>
       </c>
       <c r="P55">
-        <v>-18.66027624</v>
+        <v>-18.90730032</v>
       </c>
       <c r="Q55">
-        <v>8.73972376</v>
+        <v>8.492699679999998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1708381472060392</v>
+        <v>0.1735563677974748</v>
       </c>
       <c r="T55">
-        <v>2.88771702554363</v>
+        <v>2.950493482620665</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>-0.1190808971198426</v>
+        <v>-0.116875695321327</v>
       </c>
       <c r="W55">
-        <v>0.2638792755408589</v>
+        <v>0.2633592889567689</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5952,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>-0.425288918285152</v>
+        <v>-0.4174131975761677</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5960,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2220499452234936</v>
+        <v>0.2239499452234936</v>
       </c>
       <c r="C56">
-        <v>-30.8954387654989</v>
+        <v>-32.78221361813247</v>
       </c>
       <c r="D56">
-        <v>40.48456123450111</v>
+        <v>40.05278638186753</v>
       </c>
       <c r="E56">
-        <v>51.27000000000001</v>
+        <v>52.72500000000001</v>
       </c>
       <c r="F56">
-        <v>78.57000000000001</v>
+        <v>80.02500000000001</v>
       </c>
       <c r="G56">
         <v>7.19</v>
@@ -5996,37 +6007,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M56">
-        <v>18.526806</v>
+        <v>18.869895</v>
       </c>
       <c r="N56">
-        <v>-26.26013933333333</v>
+        <v>-26.60322833333333</v>
       </c>
       <c r="O56">
-        <v>-7.352839013333335</v>
+        <v>-7.448903933333334</v>
       </c>
       <c r="P56">
-        <v>-18.90730032</v>
+        <v>-19.1543244</v>
       </c>
       <c r="Q56">
-        <v>8.492699679999998</v>
+        <v>8.245675599999998</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1735563677974748</v>
+        <v>0.1763953981929742</v>
       </c>
       <c r="T56">
-        <v>2.950493482620665</v>
+        <v>3.01606000445668</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>-0.116875695321327</v>
+        <v>-0.114750682679121</v>
       </c>
       <c r="W56">
-        <v>0.2633592889567689</v>
+        <v>0.2628582109757368</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6034,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>-0.4174131975761677</v>
+        <v>-0.4098238667111465</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6042,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2239499452234936</v>
+        <v>0.2258499452234936</v>
       </c>
       <c r="C57">
-        <v>-32.78221361813247</v>
+        <v>-34.65987575241461</v>
       </c>
       <c r="D57">
-        <v>40.05278638186753</v>
+        <v>39.6301242475854</v>
       </c>
       <c r="E57">
-        <v>52.72500000000001</v>
+        <v>54.18000000000001</v>
       </c>
       <c r="F57">
-        <v>80.02500000000001</v>
+        <v>81.48</v>
       </c>
       <c r="G57">
         <v>7.19</v>
@@ -6078,37 +6089,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M57">
-        <v>18.869895</v>
+        <v>19.212984</v>
       </c>
       <c r="N57">
-        <v>-26.60322833333333</v>
+        <v>-26.94631733333333</v>
       </c>
       <c r="O57">
-        <v>-7.448903933333334</v>
+        <v>-7.544968853333334</v>
       </c>
       <c r="P57">
-        <v>-19.1543244</v>
+        <v>-19.40134848</v>
       </c>
       <c r="Q57">
-        <v>8.245675599999998</v>
+        <v>7.998651519999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1763953981929742</v>
+        <v>0.1793634754246327</v>
       </c>
       <c r="T57">
-        <v>3.01606000445668</v>
+        <v>3.084606822739787</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>-0.114750682679121</v>
+        <v>-0.1127015633455653</v>
       </c>
       <c r="W57">
-        <v>0.2628582109757368</v>
+        <v>0.2623750286368843</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6116,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>-0.4098238667111465</v>
+        <v>-0.4025055833770188</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6124,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2258499452234936</v>
+        <v>0.2277499452234936</v>
       </c>
       <c r="C58">
-        <v>-34.65987575241461</v>
+        <v>-36.52871064518099</v>
       </c>
       <c r="D58">
-        <v>39.6301242475854</v>
+        <v>39.21628935481901</v>
       </c>
       <c r="E58">
-        <v>54.18000000000001</v>
+        <v>55.63500000000001</v>
       </c>
       <c r="F58">
-        <v>81.48</v>
+        <v>82.935</v>
       </c>
       <c r="G58">
         <v>7.19</v>
@@ -6160,37 +6171,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M58">
-        <v>19.212984</v>
+        <v>19.556073</v>
       </c>
       <c r="N58">
-        <v>-26.94631733333333</v>
+        <v>-27.28940633333333</v>
       </c>
       <c r="O58">
-        <v>-7.544968853333334</v>
+        <v>-7.641033773333334</v>
       </c>
       <c r="P58">
-        <v>-19.40134848</v>
+        <v>-19.64837256</v>
       </c>
       <c r="Q58">
-        <v>7.998651519999999</v>
+        <v>7.75162744</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1793634754246327</v>
+        <v>0.1824696027600893</v>
       </c>
       <c r="T58">
-        <v>3.084606822739787</v>
+        <v>3.156341865129085</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>-0.1127015633455653</v>
+        <v>-0.110724342935994</v>
       </c>
       <c r="W58">
-        <v>0.2623750286368843</v>
+        <v>0.2619088000643074</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6198,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>-0.4025055833770188</v>
+        <v>-0.3954440819142642</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6206,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2277499452234936</v>
+        <v>0.2296499452234936</v>
       </c>
       <c r="C59">
-        <v>-36.52871064518099</v>
+        <v>-38.38899197220875</v>
       </c>
       <c r="D59">
-        <v>39.21628935481901</v>
+        <v>38.81100802779127</v>
       </c>
       <c r="E59">
-        <v>55.63500000000001</v>
+        <v>57.09000000000002</v>
       </c>
       <c r="F59">
-        <v>82.935</v>
+        <v>84.39000000000001</v>
       </c>
       <c r="G59">
         <v>7.19</v>
@@ -6242,37 +6253,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M59">
-        <v>19.556073</v>
+        <v>19.899162</v>
       </c>
       <c r="N59">
-        <v>-27.28940633333333</v>
+        <v>-27.63249533333333</v>
       </c>
       <c r="O59">
-        <v>-7.641033773333334</v>
+        <v>-7.737098693333334</v>
       </c>
       <c r="P59">
-        <v>-19.64837256</v>
+        <v>-19.89539664</v>
       </c>
       <c r="Q59">
-        <v>7.75162744</v>
+        <v>7.504603359999997</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1824696027600893</v>
+        <v>0.1857236409210438</v>
       </c>
       <c r="T59">
-        <v>3.156341865129085</v>
+        <v>3.231492861917872</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>-0.110724342935994</v>
+        <v>-0.1088153025405458</v>
       </c>
       <c r="W59">
-        <v>0.2619088000643074</v>
+        <v>0.2614586483390607</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6280,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>-0.3954440819142642</v>
+        <v>-0.3886260805019492</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6288,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2296499452234936</v>
+        <v>0.2315499452234936</v>
       </c>
       <c r="C60">
-        <v>-38.38899197220874</v>
+        <v>-40.24098221177019</v>
       </c>
       <c r="D60">
-        <v>38.81100802779127</v>
+        <v>38.41401778822981</v>
       </c>
       <c r="E60">
-        <v>57.09</v>
+        <v>58.545</v>
       </c>
       <c r="F60">
-        <v>84.39</v>
+        <v>85.845</v>
       </c>
       <c r="G60">
         <v>7.19</v>
@@ -6324,37 +6335,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M60">
-        <v>19.899162</v>
+        <v>20.242251</v>
       </c>
       <c r="N60">
-        <v>-27.63249533333333</v>
+        <v>-27.97558433333333</v>
       </c>
       <c r="O60">
-        <v>-7.737098693333333</v>
+        <v>-7.833163613333333</v>
       </c>
       <c r="P60">
-        <v>-19.89539664</v>
+        <v>-20.14242072</v>
       </c>
       <c r="Q60">
-        <v>7.504603360000001</v>
+        <v>7.257579280000002</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1857236409210438</v>
+        <v>0.1891364126508253</v>
       </c>
       <c r="T60">
-        <v>3.231492861917871</v>
+        <v>3.310309760989039</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>-0.1088153025405458</v>
+        <v>-0.1069709753788416</v>
       </c>
       <c r="W60">
-        <v>0.2614586483390607</v>
+        <v>0.2610237559943309</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6362,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>-0.3886260805019492</v>
+        <v>-0.3820391977815774</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6370,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2315499452234936</v>
+        <v>0.2334499452234936</v>
       </c>
       <c r="C61">
-        <v>-40.24098221177019</v>
+        <v>-42.0849332115198</v>
       </c>
       <c r="D61">
-        <v>38.41401778822981</v>
+        <v>38.0250667884802</v>
       </c>
       <c r="E61">
-        <v>58.545</v>
+        <v>60</v>
       </c>
       <c r="F61">
-        <v>85.845</v>
+        <v>87.3</v>
       </c>
       <c r="G61">
         <v>7.19</v>
@@ -6406,37 +6417,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M61">
-        <v>20.242251</v>
+        <v>20.58534</v>
       </c>
       <c r="N61">
-        <v>-27.97558433333333</v>
+        <v>-28.31867333333333</v>
       </c>
       <c r="O61">
-        <v>-7.833163613333333</v>
+        <v>-7.929228533333333</v>
       </c>
       <c r="P61">
-        <v>-20.14242072</v>
+        <v>-20.3894448</v>
       </c>
       <c r="Q61">
-        <v>7.257579280000002</v>
+        <v>7.010555200000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1891364126508253</v>
+        <v>0.192719822967096</v>
       </c>
       <c r="T61">
-        <v>3.310309760989039</v>
+        <v>3.393067505013765</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>-0.1069709753788416</v>
+        <v>-0.1051881257891943</v>
       </c>
       <c r="W61">
-        <v>0.2610237559943309</v>
+        <v>0.260603360061092</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6444,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>-0.3820391977815774</v>
+        <v>-0.375671877818551</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6452,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2334499452234936</v>
+        <v>0.2353499452234936</v>
       </c>
       <c r="C62">
-        <v>-42.0849332115198</v>
+        <v>-43.92108672128698</v>
       </c>
       <c r="D62">
-        <v>38.0250667884802</v>
+        <v>37.64391327871301</v>
       </c>
       <c r="E62">
-        <v>60</v>
+        <v>61.455</v>
       </c>
       <c r="F62">
-        <v>87.3</v>
+        <v>88.755</v>
       </c>
       <c r="G62">
         <v>7.19</v>
@@ -6488,37 +6499,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M62">
-        <v>20.58534</v>
+        <v>20.928429</v>
       </c>
       <c r="N62">
-        <v>-28.31867333333333</v>
+        <v>-28.66176233333333</v>
       </c>
       <c r="O62">
-        <v>-7.929228533333333</v>
+        <v>-8.025293453333333</v>
       </c>
       <c r="P62">
-        <v>-20.3894448</v>
+        <v>-20.63646888</v>
       </c>
       <c r="Q62">
-        <v>7.010555200000002</v>
+        <v>6.76353112</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.192719822967096</v>
+        <v>0.1964869979149702</v>
       </c>
       <c r="T62">
-        <v>3.393067505013765</v>
+        <v>3.480069235911554</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>-0.1051881257891943</v>
+        <v>-0.1034637302844534</v>
       </c>
       <c r="W62">
-        <v>0.260603360061092</v>
+        <v>0.2601967476010741</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6526,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>-0.375671877818551</v>
+        <v>-0.3695133224444764</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6534,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2353499452234936</v>
+        <v>0.2372499452234936</v>
       </c>
       <c r="C63">
-        <v>-43.92108672128698</v>
+        <v>-45.74967489414364</v>
       </c>
       <c r="D63">
-        <v>37.64391327871301</v>
+        <v>37.27032510585636</v>
       </c>
       <c r="E63">
-        <v>61.455</v>
+        <v>62.91</v>
       </c>
       <c r="F63">
-        <v>88.755</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="G63">
         <v>7.19</v>
@@ -6570,37 +6581,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M63">
-        <v>20.928429</v>
+        <v>21.271518</v>
       </c>
       <c r="N63">
-        <v>-28.66176233333333</v>
+        <v>-29.00485133333333</v>
       </c>
       <c r="O63">
-        <v>-8.025293453333333</v>
+        <v>-8.121358373333333</v>
       </c>
       <c r="P63">
-        <v>-20.63646888</v>
+        <v>-20.88349296</v>
       </c>
       <c r="Q63">
-        <v>6.76353112</v>
+        <v>6.51650704</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1964869979149702</v>
+        <v>0.2004524452285221</v>
       </c>
       <c r="T63">
-        <v>3.480069235911554</v>
+        <v>3.571650005277647</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>-0.1034637302844534</v>
+        <v>-0.1017949604411558</v>
       </c>
       <c r="W63">
-        <v>0.2601967476010741</v>
+        <v>0.2598032516720245</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6608,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>-0.3695133224444764</v>
+        <v>-0.3635534301469849</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6616,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2372499452234936</v>
+        <v>0.2391499452234936</v>
       </c>
       <c r="C64">
-        <v>-45.74967489414364</v>
+        <v>-47.5709207579285</v>
       </c>
       <c r="D64">
-        <v>37.27032510585636</v>
+        <v>36.90407924207151</v>
       </c>
       <c r="E64">
-        <v>62.91</v>
+        <v>64.36500000000001</v>
       </c>
       <c r="F64">
-        <v>90.20999999999999</v>
+        <v>91.66500000000001</v>
       </c>
       <c r="G64">
         <v>7.19</v>
@@ -6652,37 +6663,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M64">
-        <v>21.271518</v>
+        <v>21.614607</v>
       </c>
       <c r="N64">
-        <v>-29.00485133333333</v>
+        <v>-29.34794033333333</v>
       </c>
       <c r="O64">
-        <v>-8.121358373333333</v>
+        <v>-8.217423293333335</v>
       </c>
       <c r="P64">
-        <v>-20.88349296</v>
+        <v>-21.13051704</v>
       </c>
       <c r="Q64">
-        <v>6.51650704</v>
+        <v>6.269482959999998</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2004524452285221</v>
+        <v>0.2046322410455092</v>
       </c>
       <c r="T64">
-        <v>3.571650005277647</v>
+        <v>3.668181086501368</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>-0.1017949604411558</v>
+        <v>-0.1001791674182803</v>
       </c>
       <c r="W64">
-        <v>0.2598032516720245</v>
+        <v>0.2594222476772305</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6690,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>-0.3635534301469849</v>
+        <v>-0.3577827407795724</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6698,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2391499452234936</v>
+        <v>0.2410499452234936</v>
       </c>
       <c r="C65">
-        <v>-47.5709207579285</v>
+        <v>-49.38503865924044</v>
       </c>
       <c r="D65">
-        <v>36.90407924207151</v>
+        <v>36.54496134075957</v>
       </c>
       <c r="E65">
-        <v>64.36500000000001</v>
+        <v>65.82000000000001</v>
       </c>
       <c r="F65">
-        <v>91.66500000000001</v>
+        <v>93.12</v>
       </c>
       <c r="G65">
         <v>7.19</v>
@@ -6734,37 +6745,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M65">
-        <v>21.614607</v>
+        <v>21.957696</v>
       </c>
       <c r="N65">
-        <v>-29.34794033333333</v>
+        <v>-29.69102933333333</v>
       </c>
       <c r="O65">
-        <v>-8.217423293333335</v>
+        <v>-8.313488213333335</v>
       </c>
       <c r="P65">
-        <v>-21.13051704</v>
+        <v>-21.37754112</v>
       </c>
       <c r="Q65">
-        <v>6.269482959999998</v>
+        <v>6.022458880000002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2046322410455092</v>
+        <v>0.2090442477412178</v>
       </c>
       <c r="T65">
-        <v>3.668181086501368</v>
+        <v>3.77007500557085</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>-0.1001791674182803</v>
+        <v>-0.09861386792736963</v>
       </c>
       <c r="W65">
-        <v>0.2594222476772305</v>
+        <v>0.2590531500572738</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6772,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>-0.3577827407795724</v>
+        <v>-0.3521923854548916</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6780,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2410499452234936</v>
+        <v>0.2429499452234937</v>
       </c>
       <c r="C66">
-        <v>-49.38503865924044</v>
+        <v>-51.1922346817589</v>
       </c>
       <c r="D66">
-        <v>36.54496134075957</v>
+        <v>36.19276531824111</v>
       </c>
       <c r="E66">
-        <v>65.82000000000001</v>
+        <v>67.27500000000001</v>
       </c>
       <c r="F66">
-        <v>93.12</v>
+        <v>94.575</v>
       </c>
       <c r="G66">
         <v>7.19</v>
@@ -6816,37 +6827,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M66">
-        <v>21.957696</v>
+        <v>22.300785</v>
       </c>
       <c r="N66">
-        <v>-29.69102933333333</v>
+        <v>-30.03411833333333</v>
       </c>
       <c r="O66">
-        <v>-8.313488213333335</v>
+        <v>-8.409553133333334</v>
       </c>
       <c r="P66">
-        <v>-21.37754112</v>
+        <v>-21.6245652</v>
       </c>
       <c r="Q66">
-        <v>6.022458880000002</v>
+        <v>5.775434799999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2090442477412178</v>
+        <v>0.2137083691052526</v>
       </c>
       <c r="T66">
-        <v>3.77007500557085</v>
+        <v>3.877791434301447</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>-0.09861386792736963</v>
+        <v>-0.09709673149771779</v>
       </c>
       <c r="W66">
-        <v>0.2590531500572738</v>
+        <v>0.2586954092871619</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6854,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>-0.3521923854548916</v>
+        <v>-0.3467740410632778</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6862,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2429499452234937</v>
+        <v>0.2448499452234936</v>
       </c>
       <c r="C67">
-        <v>-51.1922346817589</v>
+        <v>-52.99270704060554</v>
       </c>
       <c r="D67">
-        <v>36.19276531824111</v>
+        <v>35.84729295939446</v>
       </c>
       <c r="E67">
-        <v>67.27500000000001</v>
+        <v>68.73</v>
       </c>
       <c r="F67">
-        <v>94.575</v>
+        <v>96.03</v>
       </c>
       <c r="G67">
         <v>7.19</v>
@@ -6898,37 +6909,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M67">
-        <v>22.300785</v>
+        <v>22.643874</v>
       </c>
       <c r="N67">
-        <v>-30.03411833333333</v>
+        <v>-30.37720733333333</v>
       </c>
       <c r="O67">
-        <v>-8.409553133333334</v>
+        <v>-8.505618053333334</v>
       </c>
       <c r="P67">
-        <v>-21.6245652</v>
+        <v>-21.87158927999999</v>
       </c>
       <c r="Q67">
-        <v>5.775434799999999</v>
+        <v>5.528410720000004</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2137083691052526</v>
+        <v>0.2186468505495247</v>
       </c>
       <c r="T67">
-        <v>3.877791434301447</v>
+        <v>3.991844123545606</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>-0.09709673149771779</v>
+        <v>-0.09562556889926754</v>
       </c>
       <c r="W67">
-        <v>0.2586954092871619</v>
+        <v>0.2583485091464473</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6936,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>-0.3467740410632778</v>
+        <v>-0.3415198889259554</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6944,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2448499452234936</v>
+        <v>0.2467499452234936</v>
       </c>
       <c r="C68">
-        <v>-52.99270704060554</v>
+        <v>-54.78664645433417</v>
       </c>
       <c r="D68">
-        <v>35.84729295939446</v>
+        <v>35.50835354566583</v>
       </c>
       <c r="E68">
-        <v>68.73</v>
+        <v>70.185</v>
       </c>
       <c r="F68">
-        <v>96.03</v>
+        <v>97.485</v>
       </c>
       <c r="G68">
         <v>7.19</v>
@@ -6980,37 +6991,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M68">
-        <v>22.643874</v>
+        <v>22.986963</v>
       </c>
       <c r="N68">
-        <v>-30.37720733333333</v>
+        <v>-30.72029633333333</v>
       </c>
       <c r="O68">
-        <v>-8.505618053333334</v>
+        <v>-8.601682973333332</v>
       </c>
       <c r="P68">
-        <v>-21.87158927999999</v>
+        <v>-22.11861336</v>
       </c>
       <c r="Q68">
-        <v>5.528410720000004</v>
+        <v>5.281386640000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2186468505495247</v>
+        <v>0.2238846338995103</v>
       </c>
       <c r="T68">
-        <v>3.991844123545606</v>
+        <v>4.112809096986383</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>-0.09562556889926754</v>
+        <v>-0.09419832160226355</v>
       </c>
       <c r="W68">
-        <v>0.2583485091464473</v>
+        <v>0.2580119642338137</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7018,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>-0.3415198889259554</v>
+        <v>-0.3364225771509413</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7026,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2467499452234936</v>
+        <v>0.2486499452234936</v>
       </c>
       <c r="C69">
-        <v>-54.78664645433417</v>
+        <v>-56.57423649601465</v>
       </c>
       <c r="D69">
-        <v>35.50835354566583</v>
+        <v>35.17576350398537</v>
       </c>
       <c r="E69">
-        <v>70.185</v>
+        <v>71.64000000000001</v>
       </c>
       <c r="F69">
-        <v>97.485</v>
+        <v>98.94000000000001</v>
       </c>
       <c r="G69">
         <v>7.19</v>
@@ -7062,37 +7073,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M69">
-        <v>22.986963</v>
+        <v>23.330052</v>
       </c>
       <c r="N69">
-        <v>-30.72029633333333</v>
+        <v>-31.06338533333333</v>
       </c>
       <c r="O69">
-        <v>-8.601682973333332</v>
+        <v>-8.697747893333334</v>
       </c>
       <c r="P69">
-        <v>-22.11861336</v>
+        <v>-22.36563744</v>
       </c>
       <c r="Q69">
-        <v>5.281386640000001</v>
+        <v>5.034362559999998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2238846338995103</v>
+        <v>0.22944977870887</v>
       </c>
       <c r="T69">
-        <v>4.112809096986383</v>
+        <v>4.241334381267206</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>-0.09419832160226355</v>
+        <v>-0.09281305216693614</v>
       </c>
       <c r="W69">
-        <v>0.2580119642338137</v>
+        <v>0.2576853177009635</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7100,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>-0.3364225771509413</v>
+        <v>-0.3314751863104861</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7108,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2486499452234936</v>
+        <v>0.2505499452234936</v>
       </c>
       <c r="C70">
-        <v>-56.57423649601465</v>
+        <v>-58.35565392476962</v>
       </c>
       <c r="D70">
-        <v>35.17576350398537</v>
+        <v>34.84934607523039</v>
       </c>
       <c r="E70">
-        <v>71.64000000000001</v>
+        <v>73.09500000000001</v>
       </c>
       <c r="F70">
-        <v>98.94000000000001</v>
+        <v>100.395</v>
       </c>
       <c r="G70">
         <v>7.19</v>
@@ -7144,37 +7155,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M70">
-        <v>23.330052</v>
+        <v>23.673141</v>
       </c>
       <c r="N70">
-        <v>-31.06338533333333</v>
+        <v>-31.40647433333334</v>
       </c>
       <c r="O70">
-        <v>-8.697747893333334</v>
+        <v>-8.793812813333334</v>
       </c>
       <c r="P70">
-        <v>-22.36563744</v>
+        <v>-22.61266152</v>
       </c>
       <c r="Q70">
-        <v>5.034362559999998</v>
+        <v>4.787338479999995</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.22944977870887</v>
+        <v>0.2353739651188336</v>
       </c>
       <c r="T70">
-        <v>4.241334381267206</v>
+        <v>4.378151619372601</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>-0.09281305216693614</v>
+        <v>-0.09146793546886459</v>
       </c>
       <c r="W70">
-        <v>0.2576853177009635</v>
+        <v>0.2573681391835583</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7182,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>-0.3314751863104861</v>
+        <v>-0.3266711981030879</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7190,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2505499452234936</v>
+        <v>0.2524499452234936</v>
       </c>
       <c r="C71">
-        <v>-58.35565392476962</v>
+        <v>-60.13106899902152</v>
       </c>
       <c r="D71">
-        <v>34.84934607523039</v>
+        <v>34.52893100097849</v>
       </c>
       <c r="E71">
-        <v>73.09500000000001</v>
+        <v>74.55000000000001</v>
       </c>
       <c r="F71">
-        <v>100.395</v>
+        <v>101.85</v>
       </c>
       <c r="G71">
         <v>7.19</v>
@@ -7226,37 +7237,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M71">
-        <v>23.673141</v>
+        <v>24.01623</v>
       </c>
       <c r="N71">
-        <v>-31.40647433333334</v>
+        <v>-31.74956333333333</v>
       </c>
       <c r="O71">
-        <v>-8.793812813333334</v>
+        <v>-8.889877733333334</v>
       </c>
       <c r="P71">
-        <v>-22.61266152</v>
+        <v>-22.8596856</v>
       </c>
       <c r="Q71">
-        <v>4.787338479999995</v>
+        <v>4.5403144</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2353739651188336</v>
+        <v>0.2416930972894613</v>
       </c>
       <c r="T71">
-        <v>4.378151619372601</v>
+        <v>4.524090006685021</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>-0.09146793546886459</v>
+        <v>-0.09016125067645224</v>
       </c>
       <c r="W71">
-        <v>0.2573681391835583</v>
+        <v>0.2570600229095074</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7264,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>-0.3266711981030879</v>
+        <v>-0.3220044667016151</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7272,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2524499452234936</v>
+        <v>0.2543499452234936</v>
       </c>
       <c r="C72">
-        <v>-60.13106899902152</v>
+        <v>-61.90064577261671</v>
       </c>
       <c r="D72">
-        <v>34.52893100097849</v>
+        <v>34.2143542273833</v>
       </c>
       <c r="E72">
-        <v>74.55000000000001</v>
+        <v>76.00500000000001</v>
       </c>
       <c r="F72">
-        <v>101.85</v>
+        <v>103.305</v>
       </c>
       <c r="G72">
         <v>7.19</v>
@@ -7308,37 +7319,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M72">
-        <v>24.01623</v>
+        <v>24.359319</v>
       </c>
       <c r="N72">
-        <v>-31.74956333333333</v>
+        <v>-32.09265233333333</v>
       </c>
       <c r="O72">
-        <v>-8.889877733333334</v>
+        <v>-8.985942653333334</v>
       </c>
       <c r="P72">
-        <v>-22.8596856</v>
+        <v>-23.10670968</v>
       </c>
       <c r="Q72">
-        <v>4.5403144</v>
+        <v>4.293290319999997</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2416930972894613</v>
+        <v>0.2484480316787531</v>
       </c>
       <c r="T72">
-        <v>4.524090006685021</v>
+        <v>4.680093110363815</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>-0.09016125067645224</v>
+        <v>-0.08889137390636136</v>
       </c>
       <c r="W72">
-        <v>0.2570600229095074</v>
+        <v>0.25676058596712</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7346,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>-0.3220044667016151</v>
+        <v>-0.3174691925227191</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7354,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2543499452234936</v>
+        <v>0.2562499452234936</v>
       </c>
       <c r="C73">
-        <v>-61.90064577261668</v>
+        <v>-63.66454237490846</v>
       </c>
       <c r="D73">
-        <v>34.21435422738331</v>
+        <v>33.90545762509153</v>
       </c>
       <c r="E73">
-        <v>76.005</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="F73">
-        <v>103.305</v>
+        <v>104.76</v>
       </c>
       <c r="G73">
         <v>7.19</v>
@@ -7390,37 +7401,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M73">
-        <v>24.359319</v>
+        <v>24.702408</v>
       </c>
       <c r="N73">
-        <v>-32.09265233333333</v>
+        <v>-32.43574133333333</v>
       </c>
       <c r="O73">
-        <v>-8.985942653333334</v>
+        <v>-9.082007573333332</v>
       </c>
       <c r="P73">
-        <v>-23.10670968</v>
+        <v>-23.35373375999999</v>
       </c>
       <c r="Q73">
-        <v>4.293290319999997</v>
+        <v>4.046266240000005</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2484480316787531</v>
+        <v>0.2556854613815656</v>
       </c>
       <c r="T73">
-        <v>4.680093110363813</v>
+        <v>4.847239292876806</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>-0.08889137390636137</v>
+        <v>-0.08765677149099525</v>
       </c>
       <c r="W73">
-        <v>0.25676058596712</v>
+        <v>0.2564694667175767</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7428,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>-0.3174691925227193</v>
+        <v>-0.3130598981821258</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7436,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2562499452234936</v>
+        <v>0.2581499452234937</v>
       </c>
       <c r="C74">
-        <v>-63.66454237490846</v>
+        <v>-65.422911275804</v>
       </c>
       <c r="D74">
-        <v>33.90545762509153</v>
+        <v>33.60208872419601</v>
       </c>
       <c r="E74">
-        <v>77.45999999999999</v>
+        <v>78.91500000000001</v>
       </c>
       <c r="F74">
-        <v>104.76</v>
+        <v>106.215</v>
       </c>
       <c r="G74">
         <v>7.19</v>
@@ -7472,37 +7483,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M74">
-        <v>24.702408</v>
+        <v>25.045497</v>
       </c>
       <c r="N74">
-        <v>-32.43574133333333</v>
+        <v>-32.77883033333333</v>
       </c>
       <c r="O74">
-        <v>-9.082007573333332</v>
+        <v>-9.178072493333334</v>
       </c>
       <c r="P74">
-        <v>-23.35373375999999</v>
+        <v>-23.60075784</v>
       </c>
       <c r="Q74">
-        <v>4.046266240000005</v>
+        <v>3.799242159999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2556854613815656</v>
+        <v>0.2634589969882903</v>
       </c>
       <c r="T74">
-        <v>4.847239292876806</v>
+        <v>5.026766674094467</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>-0.08765677149099525</v>
+        <v>-0.08645599379933777</v>
       </c>
       <c r="W74">
-        <v>0.2564694667175767</v>
+        <v>0.2561863233378839</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7510,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>-0.3130598981821258</v>
+        <v>-0.3087714064262064</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7518,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2581499452234937</v>
+        <v>0.2600499452234936</v>
       </c>
       <c r="C75">
-        <v>-65.422911275804</v>
+        <v>-67.1758995367082</v>
       </c>
       <c r="D75">
-        <v>33.60208872419601</v>
+        <v>33.3041004632918</v>
       </c>
       <c r="E75">
-        <v>78.91500000000001</v>
+        <v>80.37</v>
       </c>
       <c r="F75">
-        <v>106.215</v>
+        <v>107.67</v>
       </c>
       <c r="G75">
         <v>7.19</v>
@@ -7554,37 +7565,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M75">
-        <v>25.045497</v>
+        <v>25.388586</v>
       </c>
       <c r="N75">
-        <v>-32.77883033333333</v>
+        <v>-33.12191933333333</v>
       </c>
       <c r="O75">
-        <v>-9.178072493333334</v>
+        <v>-9.274137413333333</v>
       </c>
       <c r="P75">
-        <v>-23.60075784</v>
+        <v>-23.84778192</v>
       </c>
       <c r="Q75">
-        <v>3.799242159999999</v>
+        <v>3.552218080000003</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2634589969882903</v>
+        <v>0.2718304968724553</v>
       </c>
       <c r="T75">
-        <v>5.026766674094467</v>
+        <v>5.22010385386733</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>-0.08645599379933777</v>
+        <v>-0.08528766955880618</v>
       </c>
       <c r="W75">
-        <v>0.2561863233378839</v>
+        <v>0.2559108324819666</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7592,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>-0.3087714064262064</v>
+        <v>-0.3045988198528793</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7600,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2600499452234936</v>
+        <v>0.2619499452234936</v>
       </c>
       <c r="C76">
-        <v>-67.1758995367082</v>
+        <v>-68.92364904823285</v>
       </c>
       <c r="D76">
-        <v>33.3041004632918</v>
+        <v>33.01135095176716</v>
       </c>
       <c r="E76">
-        <v>80.37</v>
+        <v>81.825</v>
       </c>
       <c r="F76">
-        <v>107.67</v>
+        <v>109.125</v>
       </c>
       <c r="G76">
         <v>7.19</v>
@@ -7636,37 +7647,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M76">
-        <v>25.388586</v>
+        <v>25.731675</v>
       </c>
       <c r="N76">
-        <v>-33.12191933333333</v>
+        <v>-33.46500833333333</v>
       </c>
       <c r="O76">
-        <v>-9.274137413333333</v>
+        <v>-9.370202333333333</v>
       </c>
       <c r="P76">
-        <v>-23.84778192</v>
+        <v>-24.094806</v>
       </c>
       <c r="Q76">
-        <v>3.552218080000003</v>
+        <v>3.305194</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2718304968724553</v>
+        <v>0.2808717167473536</v>
       </c>
       <c r="T76">
-        <v>5.22010385386733</v>
+        <v>5.428908008022025</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>-0.08528766955880618</v>
+        <v>-0.08415050063135543</v>
       </c>
       <c r="W76">
-        <v>0.2559108324819666</v>
+        <v>0.2556426880488736</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7674,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>-0.3045988198528793</v>
+        <v>-0.3005375022548407</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7682,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2619499452234936</v>
+        <v>0.2638499452234936</v>
       </c>
       <c r="C77">
-        <v>-68.92364904823285</v>
+        <v>-70.66629675547748</v>
       </c>
       <c r="D77">
-        <v>33.01135095176716</v>
+        <v>32.72370324452253</v>
       </c>
       <c r="E77">
-        <v>81.825</v>
+        <v>83.28</v>
       </c>
       <c r="F77">
-        <v>109.125</v>
+        <v>110.58</v>
       </c>
       <c r="G77">
         <v>7.19</v>
@@ -7718,37 +7729,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M77">
-        <v>25.731675</v>
+        <v>26.074764</v>
       </c>
       <c r="N77">
-        <v>-33.46500833333333</v>
+        <v>-33.80809733333334</v>
       </c>
       <c r="O77">
-        <v>-9.370202333333333</v>
+        <v>-9.466267253333335</v>
       </c>
       <c r="P77">
-        <v>-24.094806</v>
+        <v>-24.34183008</v>
       </c>
       <c r="Q77">
-        <v>3.305194</v>
+        <v>3.058169919999997</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2808717167473536</v>
+        <v>0.2906663716118266</v>
       </c>
       <c r="T77">
-        <v>5.428908008022025</v>
+        <v>5.655112508356275</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>-0.08415050063135543</v>
+        <v>-0.08304325720199549</v>
       </c>
       <c r="W77">
-        <v>0.2556426880488736</v>
+        <v>0.2553816000482305</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7756,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>-0.3005375022548407</v>
+        <v>-0.2965830614356983</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7764,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2638499452234936</v>
+        <v>0.2657499452234936</v>
       </c>
       <c r="C78">
-        <v>-70.66629675547748</v>
+        <v>-72.40397487163438</v>
       </c>
       <c r="D78">
-        <v>32.72370324452253</v>
+        <v>32.44102512836562</v>
       </c>
       <c r="E78">
-        <v>83.28</v>
+        <v>84.735</v>
       </c>
       <c r="F78">
-        <v>110.58</v>
+        <v>112.035</v>
       </c>
       <c r="G78">
         <v>7.19</v>
@@ -7800,37 +7811,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M78">
-        <v>26.074764</v>
+        <v>26.417853</v>
       </c>
       <c r="N78">
-        <v>-33.80809733333334</v>
+        <v>-34.15118633333333</v>
       </c>
       <c r="O78">
-        <v>-9.466267253333335</v>
+        <v>-9.562332173333333</v>
       </c>
       <c r="P78">
-        <v>-24.34183008</v>
+        <v>-24.58885416</v>
       </c>
       <c r="Q78">
-        <v>3.058169919999997</v>
+        <v>2.811145840000002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2906663716118266</v>
+        <v>0.3013127355949495</v>
       </c>
       <c r="T78">
-        <v>5.655112508356275</v>
+        <v>5.900986965241331</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>-0.08304325720199549</v>
+        <v>-0.08196477334222931</v>
       </c>
       <c r="W78">
-        <v>0.2553816000482305</v>
+        <v>0.2551272935540977</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7838,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>-0.2965830614356983</v>
+        <v>-0.2927313333651045</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7846,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2657499452234936</v>
+        <v>0.2676499452234936</v>
       </c>
       <c r="C79">
-        <v>-72.40397487163438</v>
+        <v>-74.13681108061699</v>
       </c>
       <c r="D79">
-        <v>32.44102512836562</v>
+        <v>32.16318891938302</v>
       </c>
       <c r="E79">
-        <v>84.735</v>
+        <v>86.19000000000001</v>
       </c>
       <c r="F79">
-        <v>112.035</v>
+        <v>113.49</v>
       </c>
       <c r="G79">
         <v>7.19</v>
@@ -7882,37 +7893,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M79">
-        <v>26.417853</v>
+        <v>26.760942</v>
       </c>
       <c r="N79">
-        <v>-34.15118633333333</v>
+        <v>-34.49427533333333</v>
       </c>
       <c r="O79">
-        <v>-9.562332173333333</v>
+        <v>-9.658397093333335</v>
       </c>
       <c r="P79">
-        <v>-24.58885416</v>
+        <v>-24.83587824</v>
       </c>
       <c r="Q79">
-        <v>2.811145840000002</v>
+        <v>2.564121759999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3013127355949495</v>
+        <v>0.3129269508492655</v>
       </c>
       <c r="T79">
-        <v>5.900986965241331</v>
+        <v>6.169213645479574</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>-0.08196477334222931</v>
+        <v>-0.08091394291476482</v>
       </c>
       <c r="W79">
-        <v>0.2551272935540977</v>
+        <v>0.2548795077393015</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7920,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>-0.2927313333651045</v>
+        <v>-0.2889783675527315</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7928,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2676499452234936</v>
+        <v>0.2695499452234936</v>
       </c>
       <c r="C80">
-        <v>-74.13681108061699</v>
+        <v>-75.86492872936454</v>
       </c>
       <c r="D80">
-        <v>32.16318891938302</v>
+        <v>31.89007127063547</v>
       </c>
       <c r="E80">
-        <v>86.19000000000001</v>
+        <v>87.64500000000001</v>
       </c>
       <c r="F80">
-        <v>113.49</v>
+        <v>114.945</v>
       </c>
       <c r="G80">
         <v>7.19</v>
@@ -7964,37 +7975,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M80">
-        <v>26.760942</v>
+        <v>27.104031</v>
       </c>
       <c r="N80">
-        <v>-34.49427533333333</v>
+        <v>-34.83736433333333</v>
       </c>
       <c r="O80">
-        <v>-9.658397093333335</v>
+        <v>-9.754462013333335</v>
       </c>
       <c r="P80">
-        <v>-24.83587824</v>
+        <v>-25.08290232</v>
       </c>
       <c r="Q80">
-        <v>2.564121759999999</v>
+        <v>2.31709768</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3129269508492655</v>
+        <v>0.3256472818420876</v>
       </c>
       <c r="T80">
-        <v>6.169213645479574</v>
+        <v>6.462985723835744</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>-0.08091394291476482</v>
+        <v>-0.07988971578926148</v>
       </c>
       <c r="W80">
-        <v>0.2548795077393015</v>
+        <v>0.2546379949831079</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8002,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>-0.2889783675527315</v>
+        <v>-0.2853204135330767</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8010,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2695499452234936</v>
+        <v>0.2714499452234936</v>
       </c>
       <c r="C81">
-        <v>-75.86492872936454</v>
+        <v>-77.58844701043122</v>
       </c>
       <c r="D81">
-        <v>31.89007127063547</v>
+        <v>31.62155298956878</v>
       </c>
       <c r="E81">
-        <v>87.64500000000001</v>
+        <v>89.10000000000001</v>
       </c>
       <c r="F81">
-        <v>114.945</v>
+        <v>116.4</v>
       </c>
       <c r="G81">
         <v>7.19</v>
@@ -8046,37 +8057,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M81">
-        <v>27.104031</v>
+        <v>27.44712</v>
       </c>
       <c r="N81">
-        <v>-34.83736433333333</v>
+        <v>-35.18045333333333</v>
       </c>
       <c r="O81">
-        <v>-9.754462013333335</v>
+        <v>-9.850526933333335</v>
       </c>
       <c r="P81">
-        <v>-25.08290232</v>
+        <v>-25.3299264</v>
       </c>
       <c r="Q81">
-        <v>2.31709768</v>
+        <v>2.070073600000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3256472818420876</v>
+        <v>0.339639645934192</v>
       </c>
       <c r="T81">
-        <v>6.462985723835744</v>
+        <v>6.786135010027532</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>-0.07988971578926148</v>
+        <v>-0.07889109434189572</v>
       </c>
       <c r="W81">
-        <v>0.2546379949831079</v>
+        <v>0.254402520045819</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8084,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>-0.2853204135330767</v>
+        <v>-0.2817539083639133</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8092,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2714499452234936</v>
+        <v>0.2733499452234937</v>
       </c>
       <c r="C82">
-        <v>-77.58844701043122</v>
+        <v>-79.30748113542815</v>
       </c>
       <c r="D82">
-        <v>31.62155298956878</v>
+        <v>31.35751886457186</v>
       </c>
       <c r="E82">
-        <v>89.10000000000001</v>
+        <v>90.55500000000001</v>
       </c>
       <c r="F82">
-        <v>116.4</v>
+        <v>117.855</v>
       </c>
       <c r="G82">
         <v>7.19</v>
@@ -8128,37 +8139,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M82">
-        <v>27.44712</v>
+        <v>27.790209</v>
       </c>
       <c r="N82">
-        <v>-35.18045333333333</v>
+        <v>-35.52354233333333</v>
       </c>
       <c r="O82">
-        <v>-9.850526933333335</v>
+        <v>-9.946591853333334</v>
       </c>
       <c r="P82">
-        <v>-25.3299264</v>
+        <v>-25.57695048</v>
       </c>
       <c r="Q82">
-        <v>2.070073600000001</v>
+        <v>1.823049520000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.339639645934192</v>
+        <v>0.3551048904570443</v>
       </c>
       <c r="T82">
-        <v>6.786135010027532</v>
+        <v>7.143300010555298</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>-0.07889109434189572</v>
+        <v>-0.07791713021421799</v>
       </c>
       <c r="W82">
-        <v>0.254402520045819</v>
+        <v>0.2541728593045126</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8166,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>-0.2817539083639133</v>
+        <v>-0.2782754650507786</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8174,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2733499452234937</v>
+        <v>0.2752499452234936</v>
       </c>
       <c r="C83">
-        <v>-79.30748113542815</v>
+        <v>-81.02214249984752</v>
       </c>
       <c r="D83">
-        <v>31.35751886457186</v>
+        <v>31.09785750015248</v>
       </c>
       <c r="E83">
-        <v>90.55500000000001</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="F83">
-        <v>117.855</v>
+        <v>119.31</v>
       </c>
       <c r="G83">
         <v>7.19</v>
@@ -8210,37 +8221,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M83">
-        <v>27.790209</v>
+        <v>28.133298</v>
       </c>
       <c r="N83">
-        <v>-35.52354233333333</v>
+        <v>-35.86663133333333</v>
       </c>
       <c r="O83">
-        <v>-9.946591853333334</v>
+        <v>-10.04265677333333</v>
       </c>
       <c r="P83">
-        <v>-25.57695048</v>
+        <v>-25.82397456</v>
       </c>
       <c r="Q83">
-        <v>1.823049520000001</v>
+        <v>1.576025440000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3551048904570443</v>
+        <v>0.3722884954824356</v>
       </c>
       <c r="T83">
-        <v>7.143300010555298</v>
+        <v>7.540150011141702</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>-0.07791713021421799</v>
+        <v>-0.07696692130916656</v>
       </c>
       <c r="W83">
-        <v>0.2541728593045126</v>
+        <v>0.2539488000447015</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8248,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>-0.2782754650507786</v>
+        <v>-0.2748818618184519</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8256,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2752499452234936</v>
+        <v>0.2771499452234936</v>
       </c>
       <c r="C84">
-        <v>-81.02214249984752</v>
+        <v>-82.73253883976545</v>
       </c>
       <c r="D84">
-        <v>31.09785750015248</v>
+        <v>30.84246116023457</v>
       </c>
       <c r="E84">
-        <v>92.01000000000001</v>
+        <v>93.46500000000002</v>
       </c>
       <c r="F84">
-        <v>119.31</v>
+        <v>120.765</v>
       </c>
       <c r="G84">
         <v>7.19</v>
@@ -8292,37 +8303,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M84">
-        <v>28.133298</v>
+        <v>28.47638700000001</v>
       </c>
       <c r="N84">
-        <v>-35.86663133333333</v>
+        <v>-36.20972033333334</v>
       </c>
       <c r="O84">
-        <v>-10.04265677333333</v>
+        <v>-10.13872169333334</v>
       </c>
       <c r="P84">
-        <v>-25.82397456</v>
+        <v>-26.07099864</v>
       </c>
       <c r="Q84">
-        <v>1.576025440000002</v>
+        <v>1.329001359999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3722884954824356</v>
+        <v>0.3914937010990495</v>
       </c>
       <c r="T84">
-        <v>7.540150011141702</v>
+        <v>7.983688247091215</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>-0.07696692130916656</v>
+        <v>-0.07603960900423683</v>
       </c>
       <c r="W84">
-        <v>0.2539488000447015</v>
+        <v>0.253730139803199</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8330,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>-0.2748818618184519</v>
+        <v>-0.2715700321579886</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8338,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2771499452234936</v>
+        <v>0.2790499452234936</v>
       </c>
       <c r="C85">
-        <v>-82.73253883976545</v>
+        <v>-84.43877438088549</v>
       </c>
       <c r="D85">
-        <v>30.84246116023457</v>
+        <v>30.59122561911452</v>
       </c>
       <c r="E85">
-        <v>93.46500000000002</v>
+        <v>94.92000000000002</v>
       </c>
       <c r="F85">
-        <v>120.765</v>
+        <v>122.22</v>
       </c>
       <c r="G85">
         <v>7.19</v>
@@ -8374,37 +8385,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M85">
-        <v>28.47638700000001</v>
+        <v>28.81947600000001</v>
       </c>
       <c r="N85">
-        <v>-36.20972033333334</v>
+        <v>-36.55280933333334</v>
       </c>
       <c r="O85">
-        <v>-10.13872169333334</v>
+        <v>-10.23478661333334</v>
       </c>
       <c r="P85">
-        <v>-26.07099864</v>
+        <v>-26.31802272</v>
       </c>
       <c r="Q85">
-        <v>1.329001359999999</v>
+        <v>1.081977279999997</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3914937010990495</v>
+        <v>0.4130995574177401</v>
       </c>
       <c r="T85">
-        <v>7.983688247091215</v>
+        <v>8.482668762534416</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>-0.07603960900423683</v>
+        <v>-0.07513437556371019</v>
       </c>
       <c r="W85">
-        <v>0.253730139803199</v>
+        <v>0.2535166857579229</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8412,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>-0.2715700321579886</v>
+        <v>-0.2683370555846791</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8420,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2790499452234936</v>
+        <v>0.2809499452234936</v>
       </c>
       <c r="C86">
-        <v>-84.43877438088548</v>
+        <v>-86.14094998035702</v>
       </c>
       <c r="D86">
-        <v>30.59122561911452</v>
+        <v>30.34405001964297</v>
       </c>
       <c r="E86">
-        <v>94.92</v>
+        <v>96.375</v>
       </c>
       <c r="F86">
-        <v>122.22</v>
+        <v>123.675</v>
       </c>
       <c r="G86">
         <v>7.19</v>
@@ -8456,37 +8467,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M86">
-        <v>28.819476</v>
+        <v>29.162565</v>
       </c>
       <c r="N86">
-        <v>-36.55280933333333</v>
+        <v>-36.89589833333334</v>
       </c>
       <c r="O86">
-        <v>-10.23478661333333</v>
+        <v>-10.33085153333333</v>
       </c>
       <c r="P86">
-        <v>-26.31802271999999</v>
+        <v>-26.5650468</v>
       </c>
       <c r="Q86">
-        <v>1.081977280000004</v>
+        <v>0.8349531999999975</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4130995574177398</v>
+        <v>0.4375861945789226</v>
       </c>
       <c r="T86">
-        <v>8.482668762534411</v>
+        <v>9.04818001337004</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>-0.07513437556371021</v>
+        <v>-0.0742504417335489</v>
       </c>
       <c r="W86">
-        <v>0.2535166857579229</v>
+        <v>0.2533082541607709</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8494,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>-0.2683370555846791</v>
+        <v>-0.2651801490483892</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8502,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2809499452234936</v>
+        <v>0.2828499452234936</v>
       </c>
       <c r="C87">
-        <v>-86.14094998035702</v>
+        <v>-87.83916326177315</v>
       </c>
       <c r="D87">
-        <v>30.34405001964297</v>
+        <v>30.10083673822684</v>
       </c>
       <c r="E87">
-        <v>96.375</v>
+        <v>97.83</v>
       </c>
       <c r="F87">
-        <v>123.675</v>
+        <v>125.13</v>
       </c>
       <c r="G87">
         <v>7.19</v>
@@ -8538,37 +8549,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M87">
-        <v>29.162565</v>
+        <v>29.505654</v>
       </c>
       <c r="N87">
-        <v>-36.89589833333334</v>
+        <v>-37.23898733333333</v>
       </c>
       <c r="O87">
-        <v>-10.33085153333333</v>
+        <v>-10.42691645333333</v>
       </c>
       <c r="P87">
-        <v>-26.5650468</v>
+        <v>-26.81207087999999</v>
       </c>
       <c r="Q87">
-        <v>0.8349531999999975</v>
+        <v>0.5879291200000054</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4375861945789226</v>
+        <v>0.4655709227631313</v>
       </c>
       <c r="T87">
-        <v>9.04818001337004</v>
+        <v>9.694478585753613</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>-0.0742504417335489</v>
+        <v>-0.07338706450408905</v>
       </c>
       <c r="W87">
-        <v>0.2533082541607709</v>
+        <v>0.2531046698100642</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8576,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>-0.2651801490483892</v>
+        <v>-0.262096658943175</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8584,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2828499452234936</v>
+        <v>0.2847499452234936</v>
       </c>
       <c r="C88">
-        <v>-87.83916326177315</v>
+        <v>-89.53350874372812</v>
       </c>
       <c r="D88">
-        <v>30.10083673822684</v>
+        <v>29.86149125627187</v>
       </c>
       <c r="E88">
-        <v>97.83</v>
+        <v>99.285</v>
       </c>
       <c r="F88">
-        <v>125.13</v>
+        <v>126.585</v>
       </c>
       <c r="G88">
         <v>7.19</v>
@@ -8620,37 +8631,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M88">
-        <v>29.505654</v>
+        <v>29.848743</v>
       </c>
       <c r="N88">
-        <v>-37.23898733333333</v>
+        <v>-37.58207633333333</v>
       </c>
       <c r="O88">
-        <v>-10.42691645333333</v>
+        <v>-10.52298137333333</v>
       </c>
       <c r="P88">
-        <v>-26.81207087999999</v>
+        <v>-27.05909496</v>
       </c>
       <c r="Q88">
-        <v>0.5879291200000054</v>
+        <v>0.3409050399999991</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4655709227631313</v>
+        <v>0.4978609937449106</v>
       </c>
       <c r="T88">
-        <v>9.694478585753613</v>
+        <v>10.44020770773466</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>-0.07338706450408905</v>
+        <v>-0.07254353502703055</v>
       </c>
       <c r="W88">
-        <v>0.2531046698100642</v>
+        <v>0.2529057655593738</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8658,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>-0.262096658943175</v>
+        <v>-0.2590840536679664</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8666,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2847499452234936</v>
+        <v>0.2866499452234936</v>
       </c>
       <c r="C89">
-        <v>-89.53350874372812</v>
+        <v>-91.22407796228978</v>
       </c>
       <c r="D89">
-        <v>29.86149125627187</v>
+        <v>29.62592203771021</v>
       </c>
       <c r="E89">
-        <v>99.285</v>
+        <v>100.74</v>
       </c>
       <c r="F89">
-        <v>126.585</v>
+        <v>128.04</v>
       </c>
       <c r="G89">
         <v>7.19</v>
@@ -8702,37 +8713,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M89">
-        <v>29.848743</v>
+        <v>30.191832</v>
       </c>
       <c r="N89">
-        <v>-37.58207633333333</v>
+        <v>-37.92516533333333</v>
       </c>
       <c r="O89">
-        <v>-10.52298137333333</v>
+        <v>-10.61904629333333</v>
       </c>
       <c r="P89">
-        <v>-27.05909496</v>
+        <v>-27.30611903999999</v>
       </c>
       <c r="Q89">
-        <v>0.3409050399999991</v>
+        <v>0.09388096000000701</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4978609937449106</v>
+        <v>0.5355327432236534</v>
       </c>
       <c r="T89">
-        <v>10.44020770773466</v>
+        <v>11.31022501671255</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>-0.07254353502703055</v>
+        <v>-0.07171917667445066</v>
       </c>
       <c r="W89">
-        <v>0.2529057655593738</v>
+        <v>0.2527113818598355</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8740,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>-0.2590840536679664</v>
+        <v>-0.2561399166944665</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8748,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2866499452234936</v>
+        <v>0.2885499452234936</v>
       </c>
       <c r="C90">
-        <v>-91.22407796228978</v>
+        <v>-92.91095958772055</v>
       </c>
       <c r="D90">
-        <v>29.62592203771021</v>
+        <v>29.39404041227946</v>
       </c>
       <c r="E90">
-        <v>100.74</v>
+        <v>102.195</v>
       </c>
       <c r="F90">
-        <v>128.04</v>
+        <v>129.495</v>
       </c>
       <c r="G90">
         <v>7.19</v>
@@ -8784,37 +8795,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M90">
-        <v>30.191832</v>
+        <v>30.534921</v>
       </c>
       <c r="N90">
-        <v>-37.92516533333333</v>
+        <v>-38.26825433333333</v>
       </c>
       <c r="O90">
-        <v>-10.61904629333333</v>
+        <v>-10.71511121333333</v>
       </c>
       <c r="P90">
-        <v>-27.30611903999999</v>
+        <v>-27.55314312</v>
       </c>
       <c r="Q90">
-        <v>0.09388096000000701</v>
+        <v>-0.1531431199999993</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5355327432236534</v>
+        <v>0.5800539016985309</v>
       </c>
       <c r="T90">
-        <v>11.31022501671255</v>
+        <v>12.33842729095915</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>-0.07171917667445066</v>
+        <v>-0.07091334322867031</v>
       </c>
       <c r="W90">
-        <v>0.2527113818598355</v>
+        <v>0.2525213663333205</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8822,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>-0.2561399166944665</v>
+        <v>-0.2532619401023939</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8830,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2885499452234936</v>
+        <v>0.2904499452234935</v>
       </c>
       <c r="C91">
-        <v>-92.91095958772055</v>
+        <v>-94.59423953575941</v>
       </c>
       <c r="D91">
-        <v>29.39404041227946</v>
+        <v>29.16576046424059</v>
       </c>
       <c r="E91">
-        <v>102.195</v>
+        <v>103.65</v>
       </c>
       <c r="F91">
-        <v>129.495</v>
+        <v>130.95</v>
       </c>
       <c r="G91">
         <v>7.19</v>
@@ -8866,37 +8877,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M91">
-        <v>30.534921</v>
+        <v>30.87801000000001</v>
       </c>
       <c r="N91">
-        <v>-38.26825433333333</v>
+        <v>-38.61134333333334</v>
       </c>
       <c r="O91">
-        <v>-10.71511121333333</v>
+        <v>-10.81117613333334</v>
       </c>
       <c r="P91">
-        <v>-27.55314312</v>
+        <v>-27.8001672</v>
       </c>
       <c r="Q91">
-        <v>-0.1531431199999993</v>
+        <v>-0.4001672000000056</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5800539016985309</v>
+        <v>0.6334792918683839</v>
       </c>
       <c r="T91">
-        <v>12.33842729095915</v>
+        <v>13.57227002005506</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>-0.07091334322867031</v>
+        <v>-0.07012541719279618</v>
       </c>
       <c r="W91">
-        <v>0.2525213663333205</v>
+        <v>0.2523355733740613</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8904,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>-0.2532619401023939</v>
+        <v>-0.2504479185457007</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8912,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2904499452234935</v>
+        <v>0.2923499452234936</v>
       </c>
       <c r="C92">
-        <v>-94.59423953575941</v>
+        <v>-96.27400107375865</v>
       </c>
       <c r="D92">
-        <v>29.16576046424059</v>
+        <v>28.94099892624136</v>
       </c>
       <c r="E92">
-        <v>103.65</v>
+        <v>105.105</v>
       </c>
       <c r="F92">
-        <v>130.95</v>
+        <v>132.405</v>
       </c>
       <c r="G92">
         <v>7.19</v>
@@ -8948,37 +8959,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M92">
-        <v>30.87801000000001</v>
+        <v>31.221099</v>
       </c>
       <c r="N92">
-        <v>-38.61134333333334</v>
+        <v>-38.95443233333333</v>
       </c>
       <c r="O92">
-        <v>-10.81117613333334</v>
+        <v>-10.90724105333333</v>
       </c>
       <c r="P92">
-        <v>-27.8001672</v>
+        <v>-28.04719128</v>
       </c>
       <c r="Q92">
-        <v>-0.4001672000000056</v>
+        <v>-0.6471912799999977</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6334792918683839</v>
+        <v>0.6987769909648711</v>
       </c>
       <c r="T92">
-        <v>13.57227002005506</v>
+        <v>15.0803000222834</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>-0.07012541719279618</v>
+        <v>-0.06935480821265558</v>
       </c>
       <c r="W92">
-        <v>0.2523355733740613</v>
+        <v>0.2521538637765442</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8986,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>-0.2504479185457007</v>
+        <v>-0.2476957436166269</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8994,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2923499452234936</v>
+        <v>0.2942499452234936</v>
       </c>
       <c r="C93">
-        <v>-96.27400107375865</v>
+        <v>-97.95032492195025</v>
       </c>
       <c r="D93">
-        <v>28.94099892624136</v>
+        <v>28.71967507804976</v>
       </c>
       <c r="E93">
-        <v>105.105</v>
+        <v>106.56</v>
       </c>
       <c r="F93">
-        <v>132.405</v>
+        <v>133.86</v>
       </c>
       <c r="G93">
         <v>7.19</v>
@@ -9030,37 +9041,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M93">
-        <v>31.221099</v>
+        <v>31.56418800000001</v>
       </c>
       <c r="N93">
-        <v>-38.95443233333333</v>
+        <v>-39.29752133333334</v>
       </c>
       <c r="O93">
-        <v>-10.90724105333333</v>
+        <v>-11.00330597333333</v>
       </c>
       <c r="P93">
-        <v>-28.04719128</v>
+        <v>-28.29421536</v>
       </c>
       <c r="Q93">
-        <v>-0.6471912799999977</v>
+        <v>-0.894215360000004</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6987769909648711</v>
+        <v>0.7803991148354802</v>
       </c>
       <c r="T93">
-        <v>15.0803000222834</v>
+        <v>16.96533752506883</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>-0.06935480821265558</v>
+        <v>-0.06860095160164845</v>
       </c>
       <c r="W93">
-        <v>0.2521538637765442</v>
+        <v>0.2519761043876687</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9068,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>-0.2476957436166269</v>
+        <v>-0.2450033985773159</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9076,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2942499452234936</v>
+        <v>0.2961499452234936</v>
       </c>
       <c r="C94">
-        <v>-97.95032492195025</v>
+        <v>-99.62328935010133</v>
       </c>
       <c r="D94">
-        <v>28.71967507804976</v>
+        <v>28.50171064989867</v>
       </c>
       <c r="E94">
-        <v>106.56</v>
+        <v>108.015</v>
       </c>
       <c r="F94">
-        <v>133.86</v>
+        <v>135.315</v>
       </c>
       <c r="G94">
         <v>7.19</v>
@@ -9112,37 +9123,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M94">
-        <v>31.56418800000001</v>
+        <v>31.907277</v>
       </c>
       <c r="N94">
-        <v>-39.29752133333334</v>
+        <v>-39.64061033333333</v>
       </c>
       <c r="O94">
-        <v>-11.00330597333333</v>
+        <v>-11.09937089333333</v>
       </c>
       <c r="P94">
-        <v>-28.29421536</v>
+        <v>-28.54123943999999</v>
       </c>
       <c r="Q94">
-        <v>-0.894215360000004</v>
+        <v>-1.141239439999996</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7803991148354802</v>
+        <v>0.8853418455262633</v>
       </c>
       <c r="T94">
-        <v>16.96533752506883</v>
+        <v>19.38895717150724</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>-0.06860095160164845</v>
+        <v>-0.0678633069607705</v>
       </c>
       <c r="W94">
-        <v>0.2519761043876687</v>
+        <v>0.2518021677813497</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9150,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>-0.2450033985773159</v>
+        <v>-0.2423689534313231</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9158,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2961499452234936</v>
+        <v>0.2980499452234936</v>
       </c>
       <c r="C95">
-        <v>-99.62328935010133</v>
+        <v>-101.2929702698011</v>
       </c>
       <c r="D95">
-        <v>28.50171064989867</v>
+        <v>28.28702973019886</v>
       </c>
       <c r="E95">
-        <v>108.015</v>
+        <v>109.47</v>
       </c>
       <c r="F95">
-        <v>135.315</v>
+        <v>136.77</v>
       </c>
       <c r="G95">
         <v>7.19</v>
@@ -9194,37 +9205,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M95">
-        <v>31.907277</v>
+        <v>32.25036600000001</v>
       </c>
       <c r="N95">
-        <v>-39.64061033333333</v>
+        <v>-39.98369933333333</v>
       </c>
       <c r="O95">
-        <v>-11.09937089333333</v>
+        <v>-11.19543581333333</v>
       </c>
       <c r="P95">
-        <v>-28.54123943999999</v>
+        <v>-28.78826352</v>
       </c>
       <c r="Q95">
-        <v>-1.141239439999996</v>
+        <v>-1.388263520000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8853418455262633</v>
+        <v>1.025265486447307</v>
       </c>
       <c r="T95">
-        <v>19.38895717150724</v>
+        <v>22.62045003342512</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>-0.0678633069607705</v>
+        <v>-0.06714135688671974</v>
       </c>
       <c r="W95">
-        <v>0.2518021677813497</v>
+        <v>0.2516319319538885</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9232,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>-0.2423689534313231</v>
+        <v>-0.2397905603097132</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9240,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2980499452234936</v>
+        <v>0.2999499452234936</v>
       </c>
       <c r="C96">
-        <v>-101.2929702698011</v>
+        <v>-102.9594413226087</v>
       </c>
       <c r="D96">
-        <v>28.28702973019886</v>
+        <v>28.07555867739136</v>
       </c>
       <c r="E96">
-        <v>109.47</v>
+        <v>110.925</v>
       </c>
       <c r="F96">
-        <v>136.77</v>
+        <v>138.225</v>
       </c>
       <c r="G96">
         <v>7.19</v>
@@ -9276,37 +9287,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M96">
-        <v>32.25036600000001</v>
+        <v>32.59345500000001</v>
       </c>
       <c r="N96">
-        <v>-39.98369933333333</v>
+        <v>-40.32678833333334</v>
       </c>
       <c r="O96">
-        <v>-11.19543581333333</v>
+        <v>-11.29150073333334</v>
       </c>
       <c r="P96">
-        <v>-28.78826352</v>
+        <v>-29.0352876</v>
       </c>
       <c r="Q96">
-        <v>-1.388263520000002</v>
+        <v>-1.635287600000005</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.025265486447307</v>
+        <v>1.22115858373677</v>
       </c>
       <c r="T96">
-        <v>22.62045003342512</v>
+        <v>27.14454004011016</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>-0.06714135688671974</v>
+        <v>-0.06643460576159638</v>
       </c>
       <c r="W96">
-        <v>0.2516319319538885</v>
+        <v>0.2514652800385844</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9314,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>-0.2397905603097132</v>
+        <v>-0.2372664491485585</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9322,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2999499452234936</v>
+        <v>0.3018499452234936</v>
       </c>
       <c r="C97">
-        <v>-102.9594413226087</v>
+        <v>-104.6227739642754</v>
       </c>
       <c r="D97">
-        <v>28.07555867739136</v>
+        <v>27.86722603572458</v>
       </c>
       <c r="E97">
-        <v>110.925</v>
+        <v>112.38</v>
       </c>
       <c r="F97">
-        <v>138.225</v>
+        <v>139.68</v>
       </c>
       <c r="G97">
         <v>7.19</v>
@@ -9358,37 +9369,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M97">
-        <v>32.59345500000001</v>
+        <v>32.936544</v>
       </c>
       <c r="N97">
-        <v>-40.32678833333334</v>
+        <v>-40.66987733333333</v>
       </c>
       <c r="O97">
-        <v>-11.29150073333334</v>
+        <v>-11.38756565333333</v>
       </c>
       <c r="P97">
-        <v>-29.0352876</v>
+        <v>-29.28231168</v>
       </c>
       <c r="Q97">
-        <v>-1.635287600000005</v>
+        <v>-1.882311680000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.22115858373677</v>
+        <v>1.514998229670963</v>
       </c>
       <c r="T97">
-        <v>27.14454004011016</v>
+        <v>33.93067505013772</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>-0.06643460576159638</v>
+        <v>-0.06574257861824642</v>
       </c>
       <c r="W97">
-        <v>0.2514652800385844</v>
+        <v>0.2513021000381825</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9396,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>-0.2372664491485585</v>
+        <v>-0.2347949236365943</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9404,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3018499452234936</v>
+        <v>0.3037499452234936</v>
       </c>
       <c r="C98">
-        <v>-104.6227739642754</v>
+        <v>-106.2830375452465</v>
       </c>
       <c r="D98">
-        <v>27.8672260357246</v>
+        <v>27.66196245475347</v>
       </c>
       <c r="E98">
-        <v>112.38</v>
+        <v>113.835</v>
       </c>
       <c r="F98">
-        <v>139.68</v>
+        <v>141.135</v>
       </c>
       <c r="G98">
         <v>7.19</v>
@@ -9440,37 +9451,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M98">
-        <v>32.936544</v>
+        <v>33.279633</v>
       </c>
       <c r="N98">
-        <v>-40.66987733333333</v>
+        <v>-41.01296633333332</v>
       </c>
       <c r="O98">
-        <v>-11.38756565333333</v>
+        <v>-11.48363057333333</v>
       </c>
       <c r="P98">
-        <v>-29.28231168</v>
+        <v>-29.52933575999999</v>
       </c>
       <c r="Q98">
-        <v>-1.882311680000001</v>
+        <v>-2.129335759999993</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.514998229670959</v>
+        <v>2.004730972894611</v>
       </c>
       <c r="T98">
-        <v>33.93067505013762</v>
+        <v>45.24090006685017</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>-0.06574257861824642</v>
+        <v>-0.06506482007579029</v>
       </c>
       <c r="W98">
-        <v>0.2513021000381825</v>
+        <v>0.2511422845738714</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9478,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>-0.2347949236365943</v>
+        <v>-0.2323743574135366</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9486,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3037499452234936</v>
+        <v>0.3056499452234936</v>
       </c>
       <c r="C99">
-        <v>-106.2830375452465</v>
+        <v>-107.9402993876296</v>
       </c>
       <c r="D99">
-        <v>27.66196245475347</v>
+        <v>27.45970061237046</v>
       </c>
       <c r="E99">
-        <v>113.835</v>
+        <v>115.29</v>
       </c>
       <c r="F99">
-        <v>141.135</v>
+        <v>142.59</v>
       </c>
       <c r="G99">
         <v>7.19</v>
@@ -9522,37 +9533,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M99">
-        <v>33.279633</v>
+        <v>33.622722</v>
       </c>
       <c r="N99">
-        <v>-41.01296633333332</v>
+        <v>-41.35605533333333</v>
       </c>
       <c r="O99">
-        <v>-11.48363057333333</v>
+        <v>-11.57969549333333</v>
       </c>
       <c r="P99">
-        <v>-29.52933575999999</v>
+        <v>-29.77635984</v>
       </c>
       <c r="Q99">
-        <v>-2.129335759999993</v>
+        <v>-2.376359839999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.004730972894611</v>
+        <v>2.984196459341917</v>
       </c>
       <c r="T99">
-        <v>45.24090006685017</v>
+        <v>67.86135010027525</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>-0.06506482007579029</v>
+        <v>-0.06440089334032302</v>
       </c>
       <c r="W99">
-        <v>0.2511422845738714</v>
+        <v>0.2509857306496482</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9560,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>-0.2323743574135366</v>
+        <v>-0.2300031905011535</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9568,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3056499452234936</v>
+        <v>0.3075499452234937</v>
       </c>
       <c r="C100">
-        <v>-107.9402993876296</v>
+        <v>-109.5946248588114</v>
       </c>
       <c r="D100">
-        <v>27.45970061237046</v>
+        <v>27.26037514118856</v>
       </c>
       <c r="E100">
-        <v>115.29</v>
+        <v>116.745</v>
       </c>
       <c r="F100">
-        <v>142.59</v>
+        <v>144.045</v>
       </c>
       <c r="G100">
         <v>7.19</v>
@@ -9604,37 +9615,37 @@
         <v>-7.733333333333331</v>
       </c>
       <c r="M100">
-        <v>33.622722</v>
+        <v>33.965811</v>
       </c>
       <c r="N100">
-        <v>-41.35605533333333</v>
+        <v>-41.69914433333332</v>
       </c>
       <c r="O100">
-        <v>-11.57969549333333</v>
+        <v>-11.67576041333333</v>
       </c>
       <c r="P100">
-        <v>-29.77635984</v>
+        <v>-30.02338391999999</v>
       </c>
       <c r="Q100">
-        <v>-2.376359839999999</v>
+        <v>-2.623383919999995</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.984196459341917</v>
+        <v>5.922592918683834</v>
       </c>
       <c r="T100">
-        <v>67.86135010027525</v>
+        <v>135.7227002005505</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>-0.06440089334032302</v>
+        <v>-0.06375037926617837</v>
       </c>
       <c r="W100">
-        <v>0.2509857306496482</v>
+        <v>0.2508323394309649</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9642,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>-0.2300031905011535</v>
+        <v>-0.2276799259506368</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3075499452234937</v>
-      </c>
-      <c r="C101">
-        <v>-109.5946248588114</v>
-      </c>
-      <c r="D101">
-        <v>27.26037514118856</v>
-      </c>
-      <c r="E101">
-        <v>116.745</v>
-      </c>
-      <c r="F101">
-        <v>144.045</v>
-      </c>
-      <c r="G101">
-        <v>7.19</v>
-      </c>
-      <c r="H101">
-        <v>118.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>19.66666666666667</v>
-      </c>
-      <c r="K101">
-        <v>27.4</v>
-      </c>
-      <c r="L101">
-        <v>-7.733333333333331</v>
-      </c>
-      <c r="M101">
-        <v>33.965811</v>
-      </c>
-      <c r="N101">
-        <v>-41.69914433333332</v>
-      </c>
-      <c r="O101">
-        <v>-11.67576041333333</v>
-      </c>
-      <c r="P101">
-        <v>-30.02338391999999</v>
-      </c>
-      <c r="Q101">
-        <v>-2.623383919999995</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.922592918683834</v>
-      </c>
-      <c r="T101">
-        <v>135.7227002005505</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>-0.06375037926617837</v>
-      </c>
-      <c r="W101">
-        <v>0.2508323394309649</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>-0.2276799259506368</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
